--- a/model/Outputs/11. Interest rate/20/Output Files/0.2/Output_12_47.xlsx
+++ b/model/Outputs/11. Interest rate/20/Output Files/0.2/Output_12_47.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4153752.783347744</v>
+        <v>4154915.89952522</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13595871.02547103</v>
+        <v>13593507.14668318</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13595871.02547103</v>
+        <v>13593507.14668318</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8356.225371592229</v>
+        <v>6591.459428702124</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8356.225371592229</v>
+        <v>6591.459428702124</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>20688708.63466396</v>
+        <v>20689083.38922259</v>
       </c>
     </row>
   </sheetData>
@@ -669,7 +669,7 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G2" t="n">
-        <v>5.296708396048877</v>
+        <v>3.343301935257443</v>
       </c>
       <c r="H2" t="n">
         <v>3.769060713577687</v>
@@ -702,7 +702,7 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.953406460791602</v>
       </c>
       <c r="S2" t="n">
         <v>85.41253966161941</v>
@@ -733,16 +733,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -754,7 +754,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>167.7191059463274</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -778,7 +778,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>144.7989632036872</v>
       </c>
       <c r="R3" t="n">
         <v>133.5184388018132</v>
@@ -799,7 +799,7 @@
         <v>32.37314290982852</v>
       </c>
       <c r="X3" t="n">
-        <v>19.86273944538755</v>
+        <v>359.3926663076431</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
@@ -906,13 +906,13 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G5" t="n">
-        <v>3.343301935257416</v>
+        <v>3.343301935257443</v>
       </c>
       <c r="H5" t="n">
-        <v>3.769060713577661</v>
+        <v>3.769060713577687</v>
       </c>
       <c r="I5" t="n">
-        <v>1.95340646079149</v>
+        <v>1.953406460791434</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -942,13 +942,13 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>85.41253966161939</v>
+        <v>85.41253966161941</v>
       </c>
       <c r="T5" t="n">
-        <v>184.8629887637398</v>
+        <v>184.8629887637397</v>
       </c>
       <c r="U5" t="n">
-        <v>249.18817092047</v>
+        <v>249.1881709204699</v>
       </c>
       <c r="V5" t="n">
         <v>229.8510241668239</v>
@@ -973,16 +973,16 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>342.6720972219126</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -1018,22 +1018,22 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>133.5184388018133</v>
+        <v>133.5184388018132</v>
       </c>
       <c r="S6" t="n">
         <v>62.44885845517734</v>
       </c>
       <c r="T6" t="n">
-        <v>4.46477465147608</v>
+        <v>4.464774651476091</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1957842884886345</v>
+        <v>0.1957842884886531</v>
       </c>
       <c r="V6" t="n">
-        <v>14.51066719152016</v>
+        <v>174.422349312718</v>
       </c>
       <c r="W6" t="n">
-        <v>164.5103251158524</v>
+        <v>374</v>
       </c>
       <c r="X6" t="n">
         <v>19.86273944538755</v>
@@ -1082,7 +1082,7 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>91.51638189435316</v>
+        <v>91.51638189435317</v>
       </c>
       <c r="N7" t="n">
         <v>142.7621408454554</v>
@@ -1091,7 +1091,7 @@
         <v>214.1923837511461</v>
       </c>
       <c r="P7" t="n">
-        <v>264.9837661807365</v>
+        <v>264.9837661807364</v>
       </c>
       <c r="Q7" t="n">
         <v>310.286266425598</v>
@@ -1146,7 +1146,7 @@
         <v>3.343301935257443</v>
       </c>
       <c r="H8" t="n">
-        <v>5.722467174369123</v>
+        <v>3.769060713577687</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -1176,7 +1176,7 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.953406460791602</v>
       </c>
       <c r="S8" t="n">
         <v>85.41253966161941</v>
@@ -1207,28 +1207,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F9" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>330.0284079411381</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>209.4985557026693</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1252,10 +1252,10 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>144.7989632036872</v>
+        <v>106.0748691037268</v>
       </c>
       <c r="R9" t="n">
-        <v>293.4031483876004</v>
+        <v>133.5184388018132</v>
       </c>
       <c r="S9" t="n">
         <v>62.44885845517734</v>
@@ -1380,10 +1380,10 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G11" t="n">
-        <v>81.36239741264433</v>
+        <v>81.36239741264436</v>
       </c>
       <c r="H11" t="n">
-        <v>72.7233722713666</v>
+        <v>72.72337227136661</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1416,19 +1416,19 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>139.1041209967824</v>
+        <v>142.0601778525742</v>
       </c>
       <c r="T11" t="n">
         <v>259.5690792160011</v>
       </c>
       <c r="U11" t="n">
-        <v>328.109698558661</v>
+        <v>328.1096985586609</v>
       </c>
       <c r="V11" t="n">
         <v>308.8510241668239</v>
       </c>
       <c r="W11" t="n">
-        <v>317.3734759809475</v>
+        <v>314.4174191251561</v>
       </c>
       <c r="X11" t="n">
         <v>271.2818334606677</v>
@@ -1447,22 +1447,22 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C12" t="n">
-        <v>40.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D12" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E12" t="n">
-        <v>342.6720972219126</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F12" t="n">
-        <v>201.7955091170207</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G12" t="n">
-        <v>3.993158516536766</v>
+        <v>3.993158516536777</v>
       </c>
       <c r="H12" t="n">
-        <v>3.959653224156966</v>
+        <v>3.95965322415698</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1498,22 +1498,22 @@
         <v>131.7003678891396</v>
       </c>
       <c r="T12" t="n">
-        <v>81.34934068921194</v>
+        <v>81.34934068921193</v>
       </c>
       <c r="U12" t="n">
-        <v>79.16125598660182</v>
+        <v>79.16125598660184</v>
       </c>
       <c r="V12" t="n">
-        <v>414.5106671915202</v>
+        <v>93.51066719152016</v>
       </c>
       <c r="W12" t="n">
         <v>111.3731429098285</v>
       </c>
       <c r="X12" t="n">
-        <v>98.86273944538755</v>
+        <v>282.0220062245313</v>
       </c>
       <c r="Y12" t="n">
-        <v>78.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="13">
@@ -1553,7 +1553,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>9.517497010238174</v>
+        <v>9.517497010238188</v>
       </c>
       <c r="M13" t="n">
         <v>101.5443818943532</v>
@@ -1562,19 +1562,19 @@
         <v>154.4301408454554</v>
       </c>
       <c r="O13" t="n">
-        <v>231.000383751146</v>
+        <v>231.0003837511461</v>
       </c>
       <c r="P13" t="n">
         <v>290.7677661807365</v>
       </c>
       <c r="Q13" t="n">
-        <v>352.4422664255979</v>
+        <v>352.442266425598</v>
       </c>
       <c r="R13" t="n">
         <v>377.4666853582003</v>
       </c>
       <c r="S13" t="n">
-        <v>30.46857806351119</v>
+        <v>30.46857806351117</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -1602,7 +1602,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>158.0432560997832</v>
+        <v>160.9993129555745</v>
       </c>
       <c r="C14" t="n">
         <v>128.4745782429939</v>
@@ -1617,10 +1617,10 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G14" t="n">
-        <v>81.36239741264436</v>
+        <v>81.36239741264433</v>
       </c>
       <c r="H14" t="n">
-        <v>72.72337227136661</v>
+        <v>69.76731541560693</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1650,7 +1650,7 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>-2.424916275555106e-11</v>
       </c>
       <c r="S14" t="n">
         <v>142.0601778525742</v>
@@ -1659,7 +1659,7 @@
         <v>259.5690792160011</v>
       </c>
       <c r="U14" t="n">
-        <v>328.1096985586609</v>
+        <v>328.109698558661</v>
       </c>
       <c r="V14" t="n">
         <v>308.8510241668239</v>
@@ -1681,7 +1681,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>384.5565566463266</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C15" t="n">
         <v>40.09991244551929</v>
@@ -1696,10 +1696,10 @@
         <v>18.63624233787687</v>
       </c>
       <c r="G15" t="n">
-        <v>3.993158516536777</v>
+        <v>3.993158516536766</v>
       </c>
       <c r="H15" t="n">
-        <v>3.95965322415698</v>
+        <v>3.959653224156966</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>131.7003678891396</v>
       </c>
       <c r="T15" t="n">
-        <v>81.34934068921193</v>
+        <v>81.34934068921194</v>
       </c>
       <c r="U15" t="n">
-        <v>79.16125598660184</v>
+        <v>262.3205227657455</v>
       </c>
       <c r="V15" t="n">
-        <v>276.6699339706637</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W15" t="n">
         <v>432.3731429098285</v>
@@ -1790,7 +1790,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>9.517497010238188</v>
+        <v>9.517497010238174</v>
       </c>
       <c r="M16" t="n">
         <v>101.5443818943532</v>
@@ -1799,19 +1799,19 @@
         <v>154.4301408454554</v>
       </c>
       <c r="O16" t="n">
-        <v>231.0003837511461</v>
+        <v>231.000383751146</v>
       </c>
       <c r="P16" t="n">
         <v>290.7677661807365</v>
       </c>
       <c r="Q16" t="n">
-        <v>352.442266425598</v>
+        <v>352.4422664255979</v>
       </c>
       <c r="R16" t="n">
         <v>377.4666853582003</v>
       </c>
       <c r="S16" t="n">
-        <v>30.46857806351117</v>
+        <v>30.46857806351119</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -1857,7 +1857,7 @@
         <v>81.36239741264433</v>
       </c>
       <c r="H17" t="n">
-        <v>69.76731541558982</v>
+        <v>72.7233722713666</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -1908,7 +1908,7 @@
         <v>271.2818334606677</v>
       </c>
       <c r="Y17" t="n">
-        <v>190.3174326828064</v>
+        <v>187.3613758270147</v>
       </c>
     </row>
     <row r="18">
@@ -1918,19 +1918,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>384.5565566463266</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C18" t="n">
-        <v>361.0999124455193</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D18" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E18" t="n">
-        <v>21.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F18" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G18" t="n">
         <v>3.993158516536766</v>
@@ -1981,13 +1981,13 @@
         <v>93.51066719152016</v>
       </c>
       <c r="W18" t="n">
-        <v>294.532409688972</v>
+        <v>111.3731429098285</v>
       </c>
       <c r="X18" t="n">
-        <v>98.86273944538755</v>
+        <v>282.0220062245313</v>
       </c>
       <c r="Y18" t="n">
-        <v>399.3913927661343</v>
+        <v>78.39139276613435</v>
       </c>
     </row>
     <row r="19">
@@ -2094,7 +2094,7 @@
         <v>81.36239741264433</v>
       </c>
       <c r="H20" t="n">
-        <v>69.76731541558982</v>
+        <v>69.76731541557497</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -2155,16 +2155,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>246.7158234254704</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C21" t="n">
         <v>361.0999124455193</v>
       </c>
       <c r="D21" t="n">
-        <v>347.9376868977026</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E21" t="n">
-        <v>342.6720972219126</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F21" t="n">
         <v>18.63624233787687</v>
@@ -2221,10 +2221,10 @@
         <v>111.3731429098285</v>
       </c>
       <c r="X21" t="n">
-        <v>98.86273944538755</v>
+        <v>282.0220062245311</v>
       </c>
       <c r="Y21" t="n">
-        <v>78.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="22">
@@ -2392,13 +2392,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>384.5565566463266</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C24" t="n">
         <v>40.09991244551929</v>
       </c>
       <c r="D24" t="n">
-        <v>347.9376868977026</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E24" t="n">
         <v>21.67209722191262</v>
@@ -2449,19 +2449,19 @@
         <v>81.34934068921194</v>
       </c>
       <c r="U24" t="n">
-        <v>79.16125598660182</v>
+        <v>262.3205227657455</v>
       </c>
       <c r="V24" t="n">
-        <v>93.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W24" t="n">
-        <v>111.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X24" t="n">
-        <v>282.0220062245311</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y24" t="n">
-        <v>399.3913927661343</v>
+        <v>78.39139276613435</v>
       </c>
     </row>
     <row r="25">
@@ -2565,10 +2565,10 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G26" t="n">
-        <v>78.4063405568529</v>
+        <v>81.36239741264436</v>
       </c>
       <c r="H26" t="n">
-        <v>72.72337227136661</v>
+        <v>73.64811541557516</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -2674,10 +2674,10 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>77.80484999613995</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>285.2873461508548</v>
+        <v>179.932929367851</v>
       </c>
       <c r="S27" t="n">
         <v>131.7003678891396</v>
@@ -2689,13 +2689,13 @@
         <v>79.16125598660184</v>
       </c>
       <c r="V27" t="n">
-        <v>93.51066719152016</v>
+        <v>276.6699339706637</v>
       </c>
       <c r="W27" t="n">
-        <v>111.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X27" t="n">
-        <v>419.8627394453875</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y27" t="n">
         <v>399.3913927661343</v>
@@ -2787,7 +2787,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>158.0432560997829</v>
+        <v>160.9993129555745</v>
       </c>
       <c r="C29" t="n">
         <v>128.4745782429939</v>
@@ -2799,7 +2799,7 @@
         <v>83.36328960686865</v>
       </c>
       <c r="F29" t="n">
-        <v>83.88962870801186</v>
+        <v>84.81437185222023</v>
       </c>
       <c r="G29" t="n">
         <v>81.36239741264433</v>
@@ -2866,19 +2866,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>384.5565566463266</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C30" t="n">
         <v>40.09991244551929</v>
       </c>
       <c r="D30" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E30" t="n">
-        <v>21.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F30" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G30" t="n">
         <v>3.993158516536766</v>
@@ -2887,7 +2887,7 @@
         <v>3.959653224156966</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>105.3544167830038</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2914,7 +2914,7 @@
         <v>77.80484999613995</v>
       </c>
       <c r="R30" t="n">
-        <v>285.2873461508548</v>
+        <v>179.932929367851</v>
       </c>
       <c r="S30" t="n">
         <v>131.7003678891396</v>
@@ -2932,10 +2932,10 @@
         <v>111.3731429098285</v>
       </c>
       <c r="X30" t="n">
-        <v>419.8627394453875</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y30" t="n">
-        <v>399.3913927661343</v>
+        <v>78.39139276613435</v>
       </c>
     </row>
     <row r="31">
@@ -3039,10 +3039,10 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G32" t="n">
-        <v>81.36239741264433</v>
+        <v>81.36239741264436</v>
       </c>
       <c r="H32" t="n">
-        <v>69.76731541557497</v>
+        <v>72.72337227136661</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -3072,7 +3072,7 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>0.9247431442083234</v>
       </c>
       <c r="S32" t="n">
         <v>142.0601778525742</v>
@@ -3081,7 +3081,7 @@
         <v>259.5690792160011</v>
       </c>
       <c r="U32" t="n">
-        <v>328.109698558661</v>
+        <v>328.1096985586609</v>
       </c>
       <c r="V32" t="n">
         <v>308.8510241668239</v>
@@ -3109,7 +3109,7 @@
         <v>40.09991244551929</v>
       </c>
       <c r="D33" t="n">
-        <v>210.0969536768465</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E33" t="n">
         <v>342.6720972219126</v>
@@ -3118,10 +3118,10 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G33" t="n">
-        <v>3.993158516536766</v>
+        <v>109.3475752995406</v>
       </c>
       <c r="H33" t="n">
-        <v>3.959653224156966</v>
+        <v>3.95965322415698</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
@@ -3148,7 +3148,7 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>77.80484999613995</v>
       </c>
       <c r="R33" t="n">
         <v>179.932929367851</v>
@@ -3157,19 +3157,19 @@
         <v>131.7003678891396</v>
       </c>
       <c r="T33" t="n">
-        <v>81.34934068921194</v>
+        <v>81.34934068921193</v>
       </c>
       <c r="U33" t="n">
-        <v>79.16125598660182</v>
+        <v>79.16125598660184</v>
       </c>
       <c r="V33" t="n">
         <v>93.51066719152016</v>
       </c>
       <c r="W33" t="n">
-        <v>111.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X33" t="n">
-        <v>419.8627394453875</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y33" t="n">
         <v>78.39139276613435</v>
@@ -3212,7 +3212,7 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>9.517497010238174</v>
+        <v>9.517497010238188</v>
       </c>
       <c r="M34" t="n">
         <v>101.5443818943532</v>
@@ -3221,19 +3221,19 @@
         <v>154.4301408454554</v>
       </c>
       <c r="O34" t="n">
-        <v>231.000383751146</v>
+        <v>231.0003837511461</v>
       </c>
       <c r="P34" t="n">
         <v>290.7677661807365</v>
       </c>
       <c r="Q34" t="n">
-        <v>352.4422664255979</v>
+        <v>352.442266425598</v>
       </c>
       <c r="R34" t="n">
         <v>377.4666853582003</v>
       </c>
       <c r="S34" t="n">
-        <v>30.46857806351119</v>
+        <v>30.46857806351117</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -3261,7 +3261,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>136.9993129555745</v>
+        <v>132.4136560997828</v>
       </c>
       <c r="C35" t="n">
         <v>104.4745782429939</v>
@@ -3276,10 +3276,10 @@
         <v>59.88962870801186</v>
       </c>
       <c r="G35" t="n">
-        <v>57.36239741264435</v>
+        <v>57.36239741264433</v>
       </c>
       <c r="H35" t="n">
-        <v>48.72337227136661</v>
+        <v>48.7233722713666</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
@@ -3318,13 +3318,13 @@
         <v>235.5690792160011</v>
       </c>
       <c r="U35" t="n">
-        <v>304.1096985586609</v>
+        <v>304.109698558661</v>
       </c>
       <c r="V35" t="n">
         <v>284.8510241668239</v>
       </c>
       <c r="W35" t="n">
-        <v>288.7878191251913</v>
+        <v>293.3734759809475</v>
       </c>
       <c r="X35" t="n">
         <v>247.2818334606677</v>
@@ -3340,16 +3340,16 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>39.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C36" t="n">
-        <v>16.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D36" t="n">
-        <v>347.9376868977026</v>
+        <v>2.937686897702633</v>
       </c>
       <c r="E36" t="n">
-        <v>152.0192133867579</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
@@ -3361,7 +3361,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>191.4287443819146</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3385,31 +3385,31 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>77.80484999613995</v>
+        <v>76.25280776485613</v>
       </c>
       <c r="R36" t="n">
-        <v>500.932929367851</v>
+        <v>155.932929367851</v>
       </c>
       <c r="S36" t="n">
         <v>107.7003678891396</v>
       </c>
       <c r="T36" t="n">
-        <v>57.34934068921193</v>
+        <v>57.34934068921194</v>
       </c>
       <c r="U36" t="n">
-        <v>55.16125598660184</v>
+        <v>55.16125598660182</v>
       </c>
       <c r="V36" t="n">
         <v>69.51066719152016</v>
       </c>
       <c r="W36" t="n">
-        <v>432.3731429098285</v>
+        <v>87.37314290982852</v>
       </c>
       <c r="X36" t="n">
-        <v>74.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y36" t="n">
-        <v>54.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="37">
@@ -3452,25 +3452,25 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>77.54438189435318</v>
+        <v>77.54438189435319</v>
       </c>
       <c r="N37" t="n">
         <v>130.4301408454554</v>
       </c>
       <c r="O37" t="n">
-        <v>207.0003837511461</v>
+        <v>207.000383751146</v>
       </c>
       <c r="P37" t="n">
         <v>266.7677661807365</v>
       </c>
       <c r="Q37" t="n">
-        <v>328.442266425598</v>
+        <v>328.4422664255979</v>
       </c>
       <c r="R37" t="n">
         <v>353.4666853582003</v>
       </c>
       <c r="S37" t="n">
-        <v>6.468578063511176</v>
+        <v>6.468578063511188</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -3498,7 +3498,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>132.4136560998256</v>
+        <v>136.9993129555745</v>
       </c>
       <c r="C38" t="n">
         <v>104.4745782429939</v>
@@ -3516,7 +3516,7 @@
         <v>57.36239741264435</v>
       </c>
       <c r="H38" t="n">
-        <v>48.72337227136661</v>
+        <v>44.13771541564726</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -3546,7 +3546,7 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>-6.974588888737141e-11</v>
       </c>
       <c r="S38" t="n">
         <v>118.0601778525742</v>
@@ -3577,13 +3577,13 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>39.55655664632661</v>
+        <v>123.5010248513859</v>
       </c>
       <c r="C39" t="n">
         <v>361.0999124455193</v>
       </c>
       <c r="D39" t="n">
-        <v>2.937686897702633</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E39" t="n">
         <v>342.6720972219126</v>
@@ -3595,10 +3595,10 @@
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>159.7108738269754</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>191.4287443819146</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3622,7 +3622,7 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>77.80484999613995</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
         <v>155.932929367851</v>
@@ -3735,7 +3735,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>132.4136560998256</v>
+        <v>132.4136560997828</v>
       </c>
       <c r="C41" t="n">
         <v>104.4745782429939</v>
@@ -3750,10 +3750,10 @@
         <v>59.88962870801186</v>
       </c>
       <c r="G41" t="n">
-        <v>57.36239741264435</v>
+        <v>57.36239741264433</v>
       </c>
       <c r="H41" t="n">
-        <v>48.72337227136661</v>
+        <v>48.7233722713666</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -3792,7 +3792,7 @@
         <v>235.5690792160011</v>
       </c>
       <c r="U41" t="n">
-        <v>304.1096985586609</v>
+        <v>304.109698558661</v>
       </c>
       <c r="V41" t="n">
         <v>284.8510241668239</v>
@@ -3823,19 +3823,19 @@
         <v>2.937686897702633</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>174.387462940725</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>324.959653224157</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>191.4287443819146</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3859,28 +3859,28 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>76.25280776482641</v>
+        <v>77.80484999613995</v>
       </c>
       <c r="R42" t="n">
-        <v>500.932929367851</v>
+        <v>155.932929367851</v>
       </c>
       <c r="S42" t="n">
-        <v>452.7003678891396</v>
+        <v>107.7003678891396</v>
       </c>
       <c r="T42" t="n">
-        <v>402.3493406892119</v>
+        <v>57.34934068921194</v>
       </c>
       <c r="U42" t="n">
-        <v>55.16125598660184</v>
+        <v>55.16125598660182</v>
       </c>
       <c r="V42" t="n">
         <v>69.51066719152016</v>
       </c>
       <c r="W42" t="n">
-        <v>87.37314290982852</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X42" t="n">
-        <v>419.8627394453875</v>
+        <v>74.86273944538755</v>
       </c>
       <c r="Y42" t="n">
         <v>54.39139276613435</v>
@@ -3926,25 +3926,25 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>77.54438189435318</v>
+        <v>77.54438189435319</v>
       </c>
       <c r="N43" t="n">
         <v>130.4301408454554</v>
       </c>
       <c r="O43" t="n">
-        <v>207.0003837511461</v>
+        <v>207.000383751146</v>
       </c>
       <c r="P43" t="n">
         <v>266.7677661807365</v>
       </c>
       <c r="Q43" t="n">
-        <v>328.442266425598</v>
+        <v>328.4422664255979</v>
       </c>
       <c r="R43" t="n">
         <v>353.4666853582003</v>
       </c>
       <c r="S43" t="n">
-        <v>6.468578063511176</v>
+        <v>6.468578063511188</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
         <v>59.88962870801186</v>
       </c>
       <c r="G44" t="n">
-        <v>52.77674055689531</v>
+        <v>57.36239741264435</v>
       </c>
       <c r="H44" t="n">
         <v>48.72337227136661</v>
@@ -4041,7 +4041,7 @@
         <v>247.2818334606677</v>
       </c>
       <c r="Y44" t="n">
-        <v>166.3174326828064</v>
+        <v>161.7317758270145</v>
       </c>
     </row>
     <row r="45">
@@ -4054,25 +4054,25 @@
         <v>39.55655664632661</v>
       </c>
       <c r="C45" t="n">
-        <v>16.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D45" t="n">
-        <v>157.2848030625696</v>
+        <v>2.937686897702633</v>
       </c>
       <c r="E45" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>18.48830454455226</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>324.959653224157</v>
       </c>
       <c r="I45" t="n">
-        <v>191.4287443819146</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4099,10 +4099,10 @@
         <v>77.80484999613995</v>
       </c>
       <c r="R45" t="n">
-        <v>500.932929367851</v>
+        <v>155.932929367851</v>
       </c>
       <c r="S45" t="n">
-        <v>452.7003678891396</v>
+        <v>107.7003678891396</v>
       </c>
       <c r="T45" t="n">
         <v>57.34934068921193</v>
@@ -4114,10 +4114,10 @@
         <v>69.51066719152016</v>
       </c>
       <c r="W45" t="n">
-        <v>87.37314290982852</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X45" t="n">
-        <v>74.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y45" t="n">
         <v>54.39139276613435</v>
@@ -4297,19 +4297,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>108.8416377852028</v>
+        <v>106.8684999460195</v>
       </c>
       <c r="C2" t="n">
-        <v>58.86731632763319</v>
+        <v>56.89417848844992</v>
       </c>
       <c r="D2" t="n">
-        <v>48.42372467121926</v>
+        <v>46.450586832036</v>
       </c>
       <c r="E2" t="n">
-        <v>44.016361431958</v>
+        <v>42.04322359277474</v>
       </c>
       <c r="F2" t="n">
-        <v>39.07734253497633</v>
+        <v>37.10420469579307</v>
       </c>
       <c r="G2" t="n">
         <v>33.72713203391686</v>
@@ -4321,19 +4321,19 @@
         <v>29.92</v>
       </c>
       <c r="J2" t="n">
-        <v>30.01969029977264</v>
+        <v>268.3854385427136</v>
       </c>
       <c r="K2" t="n">
-        <v>82.16427879223495</v>
+        <v>320.5300270351759</v>
       </c>
       <c r="L2" t="n">
-        <v>146.8542517570591</v>
+        <v>385.22</v>
       </c>
       <c r="M2" t="n">
-        <v>146.8542517570591</v>
+        <v>385.22</v>
       </c>
       <c r="N2" t="n">
-        <v>385.22</v>
+        <v>755.48</v>
       </c>
       <c r="O2" t="n">
         <v>755.48</v>
@@ -4345,28 +4345,28 @@
         <v>1496</v>
       </c>
       <c r="R2" t="n">
-        <v>1496</v>
+        <v>1494.026862160817</v>
       </c>
       <c r="S2" t="n">
-        <v>1409.724707412506</v>
+        <v>1407.751569573322</v>
       </c>
       <c r="T2" t="n">
-        <v>1222.994415731961</v>
+        <v>1221.021277892777</v>
       </c>
       <c r="U2" t="n">
-        <v>971.2891925799706</v>
+        <v>969.3160547407873</v>
       </c>
       <c r="V2" t="n">
-        <v>739.1164408963101</v>
+        <v>737.1433030571268</v>
       </c>
       <c r="W2" t="n">
-        <v>498.3351520266661</v>
+        <v>496.3620141874828</v>
       </c>
       <c r="X2" t="n">
-        <v>304.1110778239714</v>
+        <v>302.1379399847881</v>
       </c>
       <c r="Y2" t="n">
-        <v>191.6692266292175</v>
+        <v>189.6960887900342</v>
       </c>
     </row>
     <row r="3">
@@ -4376,76 +4376,76 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1225.92484268314</v>
+        <v>358.7260491971879</v>
       </c>
       <c r="C3" t="n">
-        <v>1225.92484268314</v>
+        <v>358.7260491971879</v>
       </c>
       <c r="D3" t="n">
-        <v>874.4726336955616</v>
+        <v>358.7260491971879</v>
       </c>
       <c r="E3" t="n">
-        <v>528.3392021582761</v>
+        <v>358.7260491971879</v>
       </c>
       <c r="F3" t="n">
-        <v>528.3392021582761</v>
+        <v>358.7260491971879</v>
       </c>
       <c r="G3" t="n">
-        <v>199.5331529610881</v>
+        <v>29.92</v>
       </c>
       <c r="H3" t="n">
-        <v>199.5331529610881</v>
+        <v>29.92</v>
       </c>
       <c r="I3" t="n">
-        <v>30.1199146314645</v>
+        <v>29.92</v>
       </c>
       <c r="J3" t="n">
-        <v>174.7984703728012</v>
+        <v>174.5985557413367</v>
       </c>
       <c r="K3" t="n">
-        <v>399.4085458068072</v>
+        <v>399.2086311753428</v>
       </c>
       <c r="L3" t="n">
-        <v>718.3818833454036</v>
+        <v>718.1819687139391</v>
       </c>
       <c r="M3" t="n">
-        <v>860.0360750882628</v>
+        <v>859.8361604567983</v>
       </c>
       <c r="N3" t="n">
-        <v>1050.360878846775</v>
+        <v>1050.16096421531</v>
       </c>
       <c r="O3" t="n">
-        <v>1341.587921002191</v>
+        <v>1341.388006370727</v>
       </c>
       <c r="P3" t="n">
-        <v>1496</v>
+        <v>1495.800085368536</v>
       </c>
       <c r="Q3" t="n">
-        <v>1496</v>
+        <v>1349.538506374912</v>
       </c>
       <c r="R3" t="n">
-        <v>1361.132890099179</v>
+        <v>1214.671396474091</v>
       </c>
       <c r="S3" t="n">
-        <v>1298.053235093949</v>
+        <v>1151.591741468861</v>
       </c>
       <c r="T3" t="n">
-        <v>1293.54336170862</v>
+        <v>1147.081868083532</v>
       </c>
       <c r="U3" t="n">
-        <v>1293.345599801055</v>
+        <v>1146.884106175968</v>
       </c>
       <c r="V3" t="n">
-        <v>1278.688360213661</v>
+        <v>1132.226866588574</v>
       </c>
       <c r="W3" t="n">
-        <v>1245.988215860299</v>
+        <v>1099.526722235211</v>
       </c>
       <c r="X3" t="n">
-        <v>1225.92484268314</v>
+        <v>736.5038269749657</v>
       </c>
       <c r="Y3" t="n">
-        <v>1225.92484268314</v>
+        <v>736.5038269749657</v>
       </c>
     </row>
     <row r="4">
@@ -4455,31 +4455,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>522.0242660582178</v>
+        <v>456.1188393500892</v>
       </c>
       <c r="C4" t="n">
-        <v>648.0262718766536</v>
+        <v>456.1188393500892</v>
       </c>
       <c r="D4" t="n">
-        <v>648.0262718766536</v>
+        <v>456.1188393500892</v>
       </c>
       <c r="E4" t="n">
-        <v>765.8551760880666</v>
+        <v>573.9477435615022</v>
       </c>
       <c r="F4" t="n">
-        <v>784.5185955628184</v>
+        <v>698.3087161534377</v>
       </c>
       <c r="G4" t="n">
-        <v>784.5185955628184</v>
+        <v>851.8991623681918</v>
       </c>
       <c r="H4" t="n">
-        <v>784.5185955628184</v>
+        <v>1023.050610806278</v>
       </c>
       <c r="I4" t="n">
-        <v>1011.181257449721</v>
+        <v>1249.71327269318</v>
       </c>
       <c r="J4" t="n">
-        <v>1381.441257449721</v>
+        <v>1249.71327269318</v>
       </c>
       <c r="K4" t="n">
         <v>1381.441257449721</v>
@@ -4512,19 +4512,19 @@
         <v>259.2361373677321</v>
       </c>
       <c r="U4" t="n">
-        <v>259.2361373677321</v>
+        <v>456.1188393500892</v>
       </c>
       <c r="V4" t="n">
-        <v>259.2361373677321</v>
+        <v>456.1188393500892</v>
       </c>
       <c r="W4" t="n">
-        <v>259.2361373677321</v>
+        <v>456.1188393500892</v>
       </c>
       <c r="X4" t="n">
-        <v>410.2669283919256</v>
+        <v>456.1188393500892</v>
       </c>
       <c r="Y4" t="n">
-        <v>410.2669283919256</v>
+        <v>456.1188393500892</v>
       </c>
     </row>
     <row r="5">
@@ -4549,34 +4549,34 @@
         <v>39.07734253497633</v>
       </c>
       <c r="G5" t="n">
-        <v>35.70026987310015</v>
+        <v>35.70026987310013</v>
       </c>
       <c r="H5" t="n">
-        <v>31.89313783918332</v>
+        <v>31.89313783918327</v>
       </c>
       <c r="I5" t="n">
         <v>29.92</v>
       </c>
       <c r="J5" t="n">
-        <v>30.01969029977264</v>
+        <v>400.18</v>
       </c>
       <c r="K5" t="n">
-        <v>82.16427879223495</v>
+        <v>770.4399999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>146.8542517570591</v>
+        <v>835.1299729648241</v>
       </c>
       <c r="M5" t="n">
-        <v>517.114251757059</v>
+        <v>1205.389972964824</v>
       </c>
       <c r="N5" t="n">
-        <v>887.374251757059</v>
+        <v>1437.335793611129</v>
       </c>
       <c r="O5" t="n">
-        <v>1067.075793611129</v>
+        <v>1437.335793611129</v>
       </c>
       <c r="P5" t="n">
-        <v>1125.74</v>
+        <v>1496</v>
       </c>
       <c r="Q5" t="n">
         <v>1496</v>
@@ -4613,16 +4613,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1092.253026833469</v>
+        <v>719.1203429896864</v>
       </c>
       <c r="C6" t="n">
-        <v>727.505640524864</v>
+        <v>719.1203429896864</v>
       </c>
       <c r="D6" t="n">
-        <v>376.0534315372855</v>
+        <v>719.1203429896864</v>
       </c>
       <c r="E6" t="n">
-        <v>29.92</v>
+        <v>372.9869114524009</v>
       </c>
       <c r="F6" t="n">
         <v>29.92</v>
@@ -4664,7 +4664,7 @@
         <v>1360.932975467714</v>
       </c>
       <c r="S6" t="n">
-        <v>1297.853320462484</v>
+        <v>1297.853320462485</v>
       </c>
       <c r="T6" t="n">
         <v>1293.343447077155</v>
@@ -4673,16 +4673,16 @@
         <v>1293.145685169591</v>
       </c>
       <c r="V6" t="n">
-        <v>1278.488445582197</v>
+        <v>1116.961493944623</v>
       </c>
       <c r="W6" t="n">
-        <v>1112.316400010629</v>
+        <v>739.1837161668456</v>
       </c>
       <c r="X6" t="n">
-        <v>1092.253026833469</v>
+        <v>719.1203429896864</v>
       </c>
       <c r="Y6" t="n">
-        <v>1092.253026833469</v>
+        <v>719.1203429896864</v>
       </c>
     </row>
     <row r="7">
@@ -4692,34 +4692,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>253.0866383453244</v>
+        <v>576.0083476291953</v>
       </c>
       <c r="C7" t="n">
-        <v>379.0886441637601</v>
+        <v>702.0103534476311</v>
       </c>
       <c r="D7" t="n">
-        <v>492.4077882887602</v>
+        <v>815.3294975726312</v>
       </c>
       <c r="E7" t="n">
-        <v>610.2366925001733</v>
+        <v>933.1584017840443</v>
       </c>
       <c r="F7" t="n">
-        <v>734.5976650921087</v>
+        <v>1057.51937437598</v>
       </c>
       <c r="G7" t="n">
-        <v>888.1881113068629</v>
+        <v>1211.109820590734</v>
       </c>
       <c r="H7" t="n">
-        <v>1059.339559744949</v>
+        <v>1382.26126902882</v>
       </c>
       <c r="I7" t="n">
-        <v>1286.002221631852</v>
+        <v>1382.26126902882</v>
       </c>
       <c r="J7" t="n">
-        <v>1385.467095409585</v>
+        <v>1382.26126902882</v>
       </c>
       <c r="K7" t="n">
-        <v>1385.467095409585</v>
+        <v>1382.26126902882</v>
       </c>
       <c r="L7" t="n">
         <v>1385.467095409585</v>
@@ -4755,13 +4755,13 @@
         <v>29.92</v>
       </c>
       <c r="W7" t="n">
-        <v>29.92</v>
+        <v>201.8109182596774</v>
       </c>
       <c r="X7" t="n">
-        <v>29.92</v>
+        <v>352.841709283871</v>
       </c>
       <c r="Y7" t="n">
-        <v>141.3293006790323</v>
+        <v>464.2510099629032</v>
       </c>
     </row>
     <row r="8">
@@ -4771,22 +4771,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>108.8416377852028</v>
+        <v>106.8684999460195</v>
       </c>
       <c r="C8" t="n">
-        <v>58.86731632763319</v>
+        <v>56.89417848844992</v>
       </c>
       <c r="D8" t="n">
-        <v>48.42372467121926</v>
+        <v>46.450586832036</v>
       </c>
       <c r="E8" t="n">
-        <v>44.016361431958</v>
+        <v>42.04322359277474</v>
       </c>
       <c r="F8" t="n">
-        <v>39.07734253497633</v>
+        <v>37.10420469579307</v>
       </c>
       <c r="G8" t="n">
-        <v>35.70026987310013</v>
+        <v>33.72713203391686</v>
       </c>
       <c r="H8" t="n">
         <v>29.92</v>
@@ -4801,16 +4801,16 @@
         <v>82.16427879223495</v>
       </c>
       <c r="L8" t="n">
-        <v>452.4242787922349</v>
+        <v>146.8542517570591</v>
       </c>
       <c r="M8" t="n">
-        <v>822.6842787922349</v>
+        <v>517.114251757059</v>
       </c>
       <c r="N8" t="n">
-        <v>1067.075793611129</v>
+        <v>517.114251757059</v>
       </c>
       <c r="O8" t="n">
-        <v>1067.075793611129</v>
+        <v>755.48</v>
       </c>
       <c r="P8" t="n">
         <v>1125.74</v>
@@ -4819,28 +4819,28 @@
         <v>1496</v>
       </c>
       <c r="R8" t="n">
-        <v>1496</v>
+        <v>1494.026862160817</v>
       </c>
       <c r="S8" t="n">
-        <v>1409.724707412506</v>
+        <v>1407.751569573322</v>
       </c>
       <c r="T8" t="n">
-        <v>1222.994415731961</v>
+        <v>1221.021277892777</v>
       </c>
       <c r="U8" t="n">
-        <v>971.2891925799706</v>
+        <v>969.3160547407873</v>
       </c>
       <c r="V8" t="n">
-        <v>739.1164408963101</v>
+        <v>737.1433030571268</v>
       </c>
       <c r="W8" t="n">
-        <v>498.3351520266661</v>
+        <v>496.3620141874828</v>
       </c>
       <c r="X8" t="n">
-        <v>304.1110778239714</v>
+        <v>302.1379399847881</v>
       </c>
       <c r="Y8" t="n">
-        <v>191.6692266292175</v>
+        <v>189.6960887900342</v>
       </c>
     </row>
     <row r="9">
@@ -4850,25 +4850,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>917.9636424057419</v>
+        <v>740.8008178458908</v>
       </c>
       <c r="C9" t="n">
-        <v>917.9636424057419</v>
+        <v>376.0534315372855</v>
       </c>
       <c r="D9" t="n">
-        <v>917.9636424057419</v>
+        <v>376.0534315372855</v>
       </c>
       <c r="E9" t="n">
-        <v>917.9636424057419</v>
+        <v>29.92</v>
       </c>
       <c r="F9" t="n">
-        <v>574.8967309533409</v>
+        <v>29.92</v>
       </c>
       <c r="G9" t="n">
-        <v>574.8967309533409</v>
+        <v>29.92</v>
       </c>
       <c r="H9" t="n">
-        <v>241.534702729969</v>
+        <v>29.92</v>
       </c>
       <c r="I9" t="n">
         <v>29.92</v>
@@ -4895,31 +4895,31 @@
         <v>1495.800085368536</v>
       </c>
       <c r="Q9" t="n">
-        <v>1349.538506374912</v>
+        <v>1388.653752940529</v>
       </c>
       <c r="R9" t="n">
-        <v>1053.171689821781</v>
+        <v>1253.786643039707</v>
       </c>
       <c r="S9" t="n">
-        <v>990.0920348165509</v>
+        <v>1190.706988034478</v>
       </c>
       <c r="T9" t="n">
-        <v>985.5821614312216</v>
+        <v>1186.197114649148</v>
       </c>
       <c r="U9" t="n">
-        <v>985.3843995236573</v>
+        <v>1185.999352741584</v>
       </c>
       <c r="V9" t="n">
-        <v>970.7271599362632</v>
+        <v>1171.34211315419</v>
       </c>
       <c r="W9" t="n">
-        <v>938.0270155829011</v>
+        <v>1138.641968800828</v>
       </c>
       <c r="X9" t="n">
-        <v>917.9636424057419</v>
+        <v>1118.578595623669</v>
       </c>
       <c r="Y9" t="n">
-        <v>917.9636424057419</v>
+        <v>1118.578595623669</v>
       </c>
     </row>
     <row r="10">
@@ -4935,25 +4935,25 @@
         <v>1376.709106175661</v>
       </c>
       <c r="D10" t="n">
-        <v>1381.441257449721</v>
+        <v>1376.709106175661</v>
       </c>
       <c r="E10" t="n">
-        <v>1381.441257449721</v>
+        <v>1376.709106175661</v>
       </c>
       <c r="F10" t="n">
-        <v>1381.441257449721</v>
+        <v>1376.709106175661</v>
       </c>
       <c r="G10" t="n">
-        <v>1381.441257449721</v>
+        <v>1376.709106175661</v>
       </c>
       <c r="H10" t="n">
-        <v>1381.441257449721</v>
+        <v>1376.709106175661</v>
       </c>
       <c r="I10" t="n">
-        <v>1381.441257449721</v>
+        <v>1376.709106175661</v>
       </c>
       <c r="J10" t="n">
-        <v>1381.441257449721</v>
+        <v>1376.709106175661</v>
       </c>
       <c r="K10" t="n">
         <v>1381.441257449721</v>
@@ -5011,16 +5011,16 @@
         <v>596.4384060421568</v>
       </c>
       <c r="C11" t="n">
-        <v>466.6661047866073</v>
+        <v>466.6661047866074</v>
       </c>
       <c r="D11" t="n">
         <v>376.4245333322136</v>
       </c>
       <c r="E11" t="n">
-        <v>292.2191902949725</v>
+        <v>292.2191902949726</v>
       </c>
       <c r="F11" t="n">
-        <v>207.482191600011</v>
+        <v>207.4821916000111</v>
       </c>
       <c r="G11" t="n">
         <v>125.2979517892592</v>
@@ -5041,16 +5041,16 @@
         <v>1419.8180168065</v>
       </c>
       <c r="M11" t="n">
-        <v>1787.338193742671</v>
+        <v>1642.814971748371</v>
       </c>
       <c r="N11" t="n">
-        <v>1787.338193742671</v>
+        <v>1642.814971748371</v>
       </c>
       <c r="O11" t="n">
-        <v>1950.479999999998</v>
+        <v>1805.956778005698</v>
       </c>
       <c r="P11" t="n">
-        <v>2592</v>
+        <v>2004.265727912157</v>
       </c>
       <c r="Q11" t="n">
         <v>2592</v>
@@ -5059,16 +5059,16 @@
         <v>2592</v>
       </c>
       <c r="S11" t="n">
-        <v>2451.490786871937</v>
+        <v>2448.504870855986</v>
       </c>
       <c r="T11" t="n">
-        <v>2189.299797764865</v>
+        <v>2186.313881748914</v>
       </c>
       <c r="U11" t="n">
-        <v>1857.875859826824</v>
+        <v>1854.889943810873</v>
       </c>
       <c r="V11" t="n">
-        <v>1545.905128345183</v>
+        <v>1542.919212329232</v>
       </c>
       <c r="W11" t="n">
         <v>1225.325859677559</v>
@@ -5087,22 +5087,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1001.797593356413</v>
+        <v>816.7882329734396</v>
       </c>
       <c r="C12" t="n">
-        <v>961.2926312902321</v>
+        <v>452.0408466648342</v>
       </c>
       <c r="D12" t="n">
-        <v>609.8404223026537</v>
+        <v>100.5886376772558</v>
       </c>
       <c r="E12" t="n">
-        <v>263.7069907653682</v>
+        <v>78.69763038239458</v>
       </c>
       <c r="F12" t="n">
-        <v>59.87314317241791</v>
+        <v>59.87314317241794</v>
       </c>
       <c r="G12" t="n">
-        <v>55.83964972137068</v>
+        <v>55.83964972137069</v>
       </c>
       <c r="H12" t="n">
         <v>51.84</v>
@@ -5147,16 +5147,16 @@
         <v>1776.236481193986</v>
       </c>
       <c r="V12" t="n">
-        <v>1357.538837566188</v>
+        <v>1681.781261808612</v>
       </c>
       <c r="W12" t="n">
-        <v>1245.040713414846</v>
+        <v>1569.28313765727</v>
       </c>
       <c r="X12" t="n">
-        <v>1145.179360439707</v>
+        <v>1284.412424299158</v>
       </c>
       <c r="Y12" t="n">
-        <v>1065.99613542341</v>
+        <v>880.9867750404361</v>
       </c>
     </row>
     <row r="13">
@@ -5166,28 +5166,28 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>686.5872726401018</v>
+        <v>681.4588756890412</v>
       </c>
       <c r="C13" t="n">
-        <v>734.3792784585376</v>
+        <v>729.2508815074769</v>
       </c>
       <c r="D13" t="n">
-        <v>769.4884225835376</v>
+        <v>764.360025632477</v>
       </c>
       <c r="E13" t="n">
-        <v>809.1073267949506</v>
+        <v>803.97892984389</v>
       </c>
       <c r="F13" t="n">
-        <v>855.2582993868861</v>
+        <v>850.1299024358254</v>
       </c>
       <c r="G13" t="n">
-        <v>931.0743456016402</v>
+        <v>925.9459486505796</v>
       </c>
       <c r="H13" t="n">
-        <v>1027.888674039726</v>
+        <v>1022.760277088666</v>
       </c>
       <c r="I13" t="n">
-        <v>1189.441015926629</v>
+        <v>1184.312618975568</v>
       </c>
       <c r="J13" t="n">
         <v>1510.983618808348</v>
@@ -5211,10 +5211,10 @@
         <v>819.8981109568782</v>
       </c>
       <c r="Q13" t="n">
-        <v>463.8958216380924</v>
+        <v>463.8958216380923</v>
       </c>
       <c r="R13" t="n">
-        <v>82.61634147829413</v>
+        <v>82.61634147829412</v>
       </c>
       <c r="S13" t="n">
         <v>51.84</v>
@@ -5235,7 +5235,7 @@
         <v>619.8406342947774</v>
       </c>
       <c r="Y13" t="n">
-        <v>653.0399349738096</v>
+        <v>647.911538022749</v>
       </c>
     </row>
     <row r="14">
@@ -5245,22 +5245,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>596.4384060421568</v>
+        <v>593.4524900262379</v>
       </c>
       <c r="C14" t="n">
-        <v>466.6661047866074</v>
+        <v>463.6801887706885</v>
       </c>
       <c r="D14" t="n">
-        <v>376.4245333322136</v>
+        <v>373.4386173162947</v>
       </c>
       <c r="E14" t="n">
-        <v>292.2191902949726</v>
+        <v>289.2332742790537</v>
       </c>
       <c r="F14" t="n">
-        <v>207.4821916000111</v>
+        <v>204.4962755840922</v>
       </c>
       <c r="G14" t="n">
-        <v>125.2979517892592</v>
+        <v>122.3120357733403</v>
       </c>
       <c r="H14" t="n">
         <v>51.84</v>
@@ -5272,13 +5272,13 @@
         <v>134.360205073642</v>
       </c>
       <c r="K14" t="n">
-        <v>729.5731213236464</v>
+        <v>775.8802050736419</v>
       </c>
       <c r="L14" t="n">
-        <v>947.5092438362093</v>
+        <v>1417.400205073642</v>
       </c>
       <c r="M14" t="n">
-        <v>1589.029243836212</v>
+        <v>1589.029243836211</v>
       </c>
       <c r="N14" t="n">
         <v>2230.549243836214</v>
@@ -5293,28 +5293,28 @@
         <v>2592</v>
       </c>
       <c r="R14" t="n">
-        <v>2592</v>
+        <v>2592.000000000032</v>
       </c>
       <c r="S14" t="n">
-        <v>2448.504870855986</v>
+        <v>2448.504870856018</v>
       </c>
       <c r="T14" t="n">
-        <v>2186.313881748914</v>
+        <v>2186.313881748946</v>
       </c>
       <c r="U14" t="n">
-        <v>1854.889943810873</v>
+        <v>1854.889943810905</v>
       </c>
       <c r="V14" t="n">
-        <v>1542.919212329232</v>
+        <v>1542.919212329264</v>
       </c>
       <c r="W14" t="n">
-        <v>1222.339943661608</v>
+        <v>1222.339943661641</v>
       </c>
       <c r="X14" t="n">
-        <v>948.317889660934</v>
+        <v>948.3178896609661</v>
       </c>
       <c r="Y14" t="n">
-        <v>756.0780586682004</v>
+        <v>756.0780586682324</v>
       </c>
     </row>
     <row r="15">
@@ -5333,13 +5333,13 @@
         <v>100.5886376772558</v>
       </c>
       <c r="E15" t="n">
-        <v>78.69763038239458</v>
+        <v>78.69763038239455</v>
       </c>
       <c r="F15" t="n">
-        <v>59.87314317241794</v>
+        <v>59.87314317241791</v>
       </c>
       <c r="G15" t="n">
-        <v>55.83964972137069</v>
+        <v>55.83964972137068</v>
       </c>
       <c r="H15" t="n">
         <v>51.84</v>
@@ -5381,19 +5381,19 @@
         <v>1856.197345826917</v>
       </c>
       <c r="U15" t="n">
-        <v>1776.236481193986</v>
+        <v>1591.227120811013</v>
       </c>
       <c r="V15" t="n">
-        <v>1496.771901425639</v>
+        <v>1172.529477183214</v>
       </c>
       <c r="W15" t="n">
-        <v>1060.031353031873</v>
+        <v>735.7889287894482</v>
       </c>
       <c r="X15" t="n">
-        <v>635.9275758143093</v>
+        <v>311.685151571885</v>
       </c>
       <c r="Y15" t="n">
-        <v>556.744350798012</v>
+        <v>232.5019265555877</v>
       </c>
     </row>
     <row r="16">
@@ -5448,28 +5448,28 @@
         <v>819.8981109568782</v>
       </c>
       <c r="Q16" t="n">
-        <v>463.8958216380923</v>
+        <v>463.8958216380924</v>
       </c>
       <c r="R16" t="n">
-        <v>82.61634147829412</v>
+        <v>82.61634147829413</v>
       </c>
       <c r="S16" t="n">
         <v>51.84</v>
       </c>
       <c r="T16" t="n">
-        <v>159.2241526995476</v>
+        <v>164.3525496506081</v>
       </c>
       <c r="U16" t="n">
-        <v>327.5991351738998</v>
+        <v>332.7275321249604</v>
       </c>
       <c r="V16" t="n">
-        <v>448.2105280598458</v>
+        <v>453.3389250109063</v>
       </c>
       <c r="W16" t="n">
-        <v>541.8914463195232</v>
+        <v>547.0198432705838</v>
       </c>
       <c r="X16" t="n">
-        <v>614.7122373437168</v>
+        <v>619.8406342947774</v>
       </c>
       <c r="Y16" t="n">
         <v>647.911538022749</v>
@@ -5482,22 +5482,22 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>593.4524900262206</v>
+        <v>596.4384060421568</v>
       </c>
       <c r="C17" t="n">
-        <v>463.6801887706712</v>
+        <v>466.6661047866073</v>
       </c>
       <c r="D17" t="n">
-        <v>373.4386173162774</v>
+        <v>376.4245333322136</v>
       </c>
       <c r="E17" t="n">
-        <v>289.2332742790364</v>
+        <v>292.2191902949725</v>
       </c>
       <c r="F17" t="n">
-        <v>204.4962755840749</v>
+        <v>207.482191600011</v>
       </c>
       <c r="G17" t="n">
-        <v>122.3120357733231</v>
+        <v>125.2979517892592</v>
       </c>
       <c r="H17" t="n">
         <v>51.84</v>
@@ -5506,16 +5506,16 @@
         <v>51.84</v>
       </c>
       <c r="J17" t="n">
-        <v>560.3618942939371</v>
+        <v>134.360205073642</v>
       </c>
       <c r="K17" t="n">
-        <v>1201.881894293937</v>
+        <v>310.0317798977626</v>
       </c>
       <c r="L17" t="n">
-        <v>1419.8180168065</v>
+        <v>947.5092438362057</v>
       </c>
       <c r="M17" t="n">
-        <v>1589.029243836211</v>
+        <v>1589.02924383621</v>
       </c>
       <c r="N17" t="n">
         <v>2230.549243836214</v>
@@ -5530,28 +5530,28 @@
         <v>2592</v>
       </c>
       <c r="R17" t="n">
-        <v>2592.000000000015</v>
+        <v>2592</v>
       </c>
       <c r="S17" t="n">
-        <v>2448.504870856001</v>
+        <v>2448.504870855986</v>
       </c>
       <c r="T17" t="n">
-        <v>2186.313881748929</v>
+        <v>2186.313881748914</v>
       </c>
       <c r="U17" t="n">
-        <v>1854.889943810887</v>
+        <v>1854.889943810872</v>
       </c>
       <c r="V17" t="n">
-        <v>1542.919212329247</v>
+        <v>1542.919212329232</v>
       </c>
       <c r="W17" t="n">
-        <v>1222.339943661623</v>
+        <v>1222.339943661608</v>
       </c>
       <c r="X17" t="n">
-        <v>948.3178896609488</v>
+        <v>948.3178896609338</v>
       </c>
       <c r="Y17" t="n">
-        <v>756.0780586682151</v>
+        <v>759.0639746841513</v>
       </c>
     </row>
     <row r="18">
@@ -5561,16 +5561,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>492.5458087310153</v>
+        <v>1141.030657215864</v>
       </c>
       <c r="C18" t="n">
-        <v>127.79842242241</v>
+        <v>1100.525695149683</v>
       </c>
       <c r="D18" t="n">
-        <v>100.5886376772558</v>
+        <v>749.0734861621042</v>
       </c>
       <c r="E18" t="n">
-        <v>78.69763038239455</v>
+        <v>402.9400546248188</v>
       </c>
       <c r="F18" t="n">
         <v>59.87314317241791</v>
@@ -5624,13 +5624,13 @@
         <v>1681.781261808612</v>
       </c>
       <c r="W18" t="n">
-        <v>1384.273777274297</v>
+        <v>1569.28313765727</v>
       </c>
       <c r="X18" t="n">
         <v>1284.412424299158</v>
       </c>
       <c r="Y18" t="n">
-        <v>880.9867750404362</v>
+        <v>1205.22919928286</v>
       </c>
     </row>
     <row r="19">
@@ -5719,22 +5719,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>593.4524900262206</v>
+        <v>593.4524900262056</v>
       </c>
       <c r="C20" t="n">
-        <v>463.6801887706712</v>
+        <v>463.6801887706562</v>
       </c>
       <c r="D20" t="n">
-        <v>373.4386173162774</v>
+        <v>373.4386173162624</v>
       </c>
       <c r="E20" t="n">
-        <v>289.2332742790364</v>
+        <v>289.2332742790214</v>
       </c>
       <c r="F20" t="n">
-        <v>204.4962755840749</v>
+        <v>204.4962755840599</v>
       </c>
       <c r="G20" t="n">
-        <v>122.3120357733231</v>
+        <v>122.3120357733081</v>
       </c>
       <c r="H20" t="n">
         <v>51.84</v>
@@ -5743,52 +5743,52 @@
         <v>51.84</v>
       </c>
       <c r="J20" t="n">
-        <v>560.3618942939371</v>
+        <v>134.360205073642</v>
       </c>
       <c r="K20" t="n">
-        <v>1201.881894293937</v>
+        <v>310.0317798977626</v>
       </c>
       <c r="L20" t="n">
-        <v>1419.8180168065</v>
+        <v>947.5092438362057</v>
       </c>
       <c r="M20" t="n">
-        <v>1642.814971748371</v>
+        <v>1589.02924383621</v>
       </c>
       <c r="N20" t="n">
-        <v>1642.814971748371</v>
+        <v>2230.549243836214</v>
       </c>
       <c r="O20" t="n">
-        <v>1805.956778005698</v>
+        <v>2393.691050093541</v>
       </c>
       <c r="P20" t="n">
-        <v>2004.265727912157</v>
+        <v>2592</v>
       </c>
       <c r="Q20" t="n">
         <v>2592</v>
       </c>
       <c r="R20" t="n">
-        <v>2592.000000000015</v>
+        <v>2592</v>
       </c>
       <c r="S20" t="n">
-        <v>2448.504870856001</v>
+        <v>2448.504870855986</v>
       </c>
       <c r="T20" t="n">
-        <v>2186.313881748929</v>
+        <v>2186.313881748914</v>
       </c>
       <c r="U20" t="n">
-        <v>1854.889943810887</v>
+        <v>1854.889943810872</v>
       </c>
       <c r="V20" t="n">
-        <v>1542.919212329247</v>
+        <v>1542.919212329232</v>
       </c>
       <c r="W20" t="n">
-        <v>1222.339943661623</v>
+        <v>1222.339943661608</v>
       </c>
       <c r="X20" t="n">
-        <v>948.3178896609488</v>
+        <v>948.3178896609338</v>
       </c>
       <c r="Y20" t="n">
-        <v>756.0780586682151</v>
+        <v>756.0780586682001</v>
       </c>
     </row>
     <row r="21">
@@ -5798,13 +5798,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1141.030657215864</v>
+        <v>492.5458087310153</v>
       </c>
       <c r="C21" t="n">
-        <v>776.2832709072585</v>
+        <v>127.79842242241</v>
       </c>
       <c r="D21" t="n">
-        <v>424.8310619196801</v>
+        <v>100.5886376772558</v>
       </c>
       <c r="E21" t="n">
         <v>78.69763038239455</v>
@@ -5864,10 +5864,10 @@
         <v>1569.28313765727</v>
       </c>
       <c r="X21" t="n">
-        <v>1469.421784682131</v>
+        <v>1284.412424299158</v>
       </c>
       <c r="Y21" t="n">
-        <v>1390.238559665834</v>
+        <v>880.9867750404362</v>
       </c>
     </row>
     <row r="22">
@@ -5886,19 +5886,19 @@
         <v>769.4884225835376</v>
       </c>
       <c r="E22" t="n">
-        <v>809.1073267949506</v>
+        <v>803.97892984389</v>
       </c>
       <c r="F22" t="n">
-        <v>855.2582993868861</v>
+        <v>850.1299024358254</v>
       </c>
       <c r="G22" t="n">
-        <v>931.0743456016402</v>
+        <v>925.9459486505796</v>
       </c>
       <c r="H22" t="n">
-        <v>1027.888674039726</v>
+        <v>1022.760277088666</v>
       </c>
       <c r="I22" t="n">
-        <v>1189.441015926629</v>
+        <v>1184.312618975568</v>
       </c>
       <c r="J22" t="n">
         <v>1510.983618808348</v>
@@ -5980,25 +5980,25 @@
         <v>51.84</v>
       </c>
       <c r="J23" t="n">
-        <v>134.360205073642</v>
+        <v>560.3618942939371</v>
       </c>
       <c r="K23" t="n">
-        <v>775.8802050736419</v>
+        <v>736.0334691180577</v>
       </c>
       <c r="L23" t="n">
-        <v>1417.400205073642</v>
+        <v>953.9695916306206</v>
       </c>
       <c r="M23" t="n">
-        <v>1417.400205073642</v>
+        <v>1595.489591630625</v>
       </c>
       <c r="N23" t="n">
-        <v>2058.920205073645</v>
+        <v>1642.814971748371</v>
       </c>
       <c r="O23" t="n">
-        <v>2222.062011330972</v>
+        <v>1805.956778005698</v>
       </c>
       <c r="P23" t="n">
-        <v>2420.370961237431</v>
+        <v>2004.265727912157</v>
       </c>
       <c r="Q23" t="n">
         <v>2592</v>
@@ -6035,10 +6035,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>492.5458087310154</v>
+        <v>168.3033844885911</v>
       </c>
       <c r="C24" t="n">
-        <v>452.0408466648342</v>
+        <v>127.79842242241</v>
       </c>
       <c r="D24" t="n">
         <v>100.5886376772558</v>
@@ -6092,19 +6092,19 @@
         <v>1856.197345826917</v>
       </c>
       <c r="U24" t="n">
-        <v>1776.236481193986</v>
+        <v>1591.227120811013</v>
       </c>
       <c r="V24" t="n">
-        <v>1681.781261808612</v>
+        <v>1172.529477183214</v>
       </c>
       <c r="W24" t="n">
-        <v>1569.28313765727</v>
+        <v>735.7889287894482</v>
       </c>
       <c r="X24" t="n">
-        <v>1284.412424299158</v>
+        <v>311.685151571885</v>
       </c>
       <c r="Y24" t="n">
-        <v>880.9867750404362</v>
+        <v>232.5019265555877</v>
       </c>
     </row>
     <row r="25">
@@ -6193,76 +6193,76 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>593.4524900262059</v>
+        <v>597.4524900262059</v>
       </c>
       <c r="C26" t="n">
-        <v>463.6801887706564</v>
+        <v>467.6801887706564</v>
       </c>
       <c r="D26" t="n">
-        <v>373.4386173162627</v>
+        <v>377.4386173162627</v>
       </c>
       <c r="E26" t="n">
-        <v>289.2332742790216</v>
+        <v>293.2332742790216</v>
       </c>
       <c r="F26" t="n">
-        <v>204.4962755840601</v>
+        <v>208.4962755840601</v>
       </c>
       <c r="G26" t="n">
-        <v>125.2979517892592</v>
+        <v>126.3120357733083</v>
       </c>
       <c r="H26" t="n">
-        <v>51.84</v>
+        <v>51.92</v>
       </c>
       <c r="I26" t="n">
-        <v>51.84</v>
+        <v>51.92</v>
       </c>
       <c r="J26" t="n">
-        <v>134.360205073642</v>
+        <v>560.4418942939371</v>
       </c>
       <c r="K26" t="n">
-        <v>775.8802050736419</v>
+        <v>1004.304971748371</v>
       </c>
       <c r="L26" t="n">
-        <v>1417.400205073642</v>
+        <v>1646.814971748371</v>
       </c>
       <c r="M26" t="n">
-        <v>1589.029243836214</v>
+        <v>1646.814971748371</v>
       </c>
       <c r="N26" t="n">
-        <v>2230.549243836214</v>
+        <v>1646.814971748371</v>
       </c>
       <c r="O26" t="n">
-        <v>2393.691050093541</v>
+        <v>1809.956778005698</v>
       </c>
       <c r="P26" t="n">
-        <v>2592</v>
+        <v>2008.265727912157</v>
       </c>
       <c r="Q26" t="n">
-        <v>2592</v>
+        <v>2596</v>
       </c>
       <c r="R26" t="n">
-        <v>2592</v>
+        <v>2596</v>
       </c>
       <c r="S26" t="n">
-        <v>2448.504870855986</v>
+        <v>2452.504870855986</v>
       </c>
       <c r="T26" t="n">
-        <v>2186.313881748914</v>
+        <v>2190.313881748914</v>
       </c>
       <c r="U26" t="n">
-        <v>1854.889943810873</v>
+        <v>1858.889943810873</v>
       </c>
       <c r="V26" t="n">
-        <v>1542.919212329232</v>
+        <v>1546.919212329232</v>
       </c>
       <c r="W26" t="n">
-        <v>1222.339943661608</v>
+        <v>1226.339943661608</v>
       </c>
       <c r="X26" t="n">
-        <v>948.317889660934</v>
+        <v>952.317889660934</v>
       </c>
       <c r="Y26" t="n">
-        <v>756.0780586682004</v>
+        <v>760.0780586682004</v>
       </c>
     </row>
     <row r="27">
@@ -6272,76 +6272,76 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>492.5458087310154</v>
+        <v>492.6258087310154</v>
       </c>
       <c r="C27" t="n">
-        <v>452.0408466648343</v>
+        <v>452.1208466648343</v>
       </c>
       <c r="D27" t="n">
-        <v>424.8310619196801</v>
+        <v>424.9110619196801</v>
       </c>
       <c r="E27" t="n">
-        <v>402.9400546248189</v>
+        <v>403.0200546248188</v>
       </c>
       <c r="F27" t="n">
-        <v>59.87314317241794</v>
+        <v>59.95314317241794</v>
       </c>
       <c r="G27" t="n">
-        <v>55.83964972137069</v>
+        <v>55.91964972137069</v>
       </c>
       <c r="H27" t="n">
-        <v>51.84</v>
+        <v>51.92</v>
       </c>
       <c r="I27" t="n">
-        <v>51.84</v>
+        <v>51.92</v>
       </c>
       <c r="J27" t="n">
-        <v>245.6076497036009</v>
+        <v>245.6876497036009</v>
       </c>
       <c r="K27" t="n">
-        <v>554.1188055149654</v>
+        <v>554.1988055149654</v>
       </c>
       <c r="L27" t="n">
-        <v>985.9074996573354</v>
+        <v>985.9874996573354</v>
       </c>
       <c r="M27" t="n">
-        <v>1259.211891400195</v>
+        <v>1259.291891400195</v>
       </c>
       <c r="N27" t="n">
-        <v>1584.67128421531</v>
+        <v>1584.75128421531</v>
       </c>
       <c r="O27" t="n">
-        <v>1999.520074672614</v>
+        <v>1999.600074672614</v>
       </c>
       <c r="P27" t="n">
-        <v>2253.149505368536</v>
+        <v>2253.229505368536</v>
       </c>
       <c r="Q27" t="n">
-        <v>2174.558747796677</v>
+        <v>2253.229505368536</v>
       </c>
       <c r="R27" t="n">
-        <v>1886.389711280662</v>
+        <v>2071.479071663636</v>
       </c>
       <c r="S27" t="n">
-        <v>1753.359036645168</v>
+        <v>1938.448397028141</v>
       </c>
       <c r="T27" t="n">
-        <v>1671.187985443944</v>
+        <v>1856.277345826917</v>
       </c>
       <c r="U27" t="n">
-        <v>1591.227120811013</v>
+        <v>1776.316481193986</v>
       </c>
       <c r="V27" t="n">
-        <v>1496.771901425639</v>
+        <v>1496.851901425639</v>
       </c>
       <c r="W27" t="n">
-        <v>1384.273777274297</v>
+        <v>1060.111353031873</v>
       </c>
       <c r="X27" t="n">
-        <v>960.1700000567336</v>
+        <v>960.2500000567336</v>
       </c>
       <c r="Y27" t="n">
-        <v>556.744350798012</v>
+        <v>556.824350798012</v>
       </c>
     </row>
     <row r="28">
@@ -6351,76 +6351,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>686.5872726401018</v>
+        <v>686.6672726401017</v>
       </c>
       <c r="C28" t="n">
-        <v>734.3792784585376</v>
+        <v>734.4592784585375</v>
       </c>
       <c r="D28" t="n">
-        <v>769.4884225835376</v>
+        <v>769.5684225835375</v>
       </c>
       <c r="E28" t="n">
-        <v>809.1073267949506</v>
+        <v>809.1873267949505</v>
       </c>
       <c r="F28" t="n">
-        <v>855.2582993868861</v>
+        <v>855.338299386886</v>
       </c>
       <c r="G28" t="n">
-        <v>931.0743456016402</v>
+        <v>926.0259486505795</v>
       </c>
       <c r="H28" t="n">
-        <v>1027.888674039726</v>
+        <v>1022.840277088666</v>
       </c>
       <c r="I28" t="n">
-        <v>1189.441015926629</v>
+        <v>1184.392618975568</v>
       </c>
       <c r="J28" t="n">
-        <v>1510.983618808348</v>
+        <v>1511.063618808347</v>
       </c>
       <c r="K28" t="n">
-        <v>1615.110403564888</v>
+        <v>1615.190403564888</v>
       </c>
       <c r="L28" t="n">
-        <v>1605.496770221213</v>
+        <v>1605.576770221213</v>
       </c>
       <c r="M28" t="n">
-        <v>1502.926687499644</v>
+        <v>1503.006687499644</v>
       </c>
       <c r="N28" t="n">
-        <v>1346.936646241608</v>
+        <v>1347.016646241608</v>
       </c>
       <c r="O28" t="n">
-        <v>1113.602925280855</v>
+        <v>1113.682925280855</v>
       </c>
       <c r="P28" t="n">
-        <v>819.8981109568782</v>
+        <v>819.9781109568783</v>
       </c>
       <c r="Q28" t="n">
-        <v>463.8958216380923</v>
+        <v>463.9758216380924</v>
       </c>
       <c r="R28" t="n">
-        <v>82.61634147829412</v>
+        <v>82.69634147829412</v>
       </c>
       <c r="S28" t="n">
-        <v>51.84</v>
+        <v>51.92</v>
       </c>
       <c r="T28" t="n">
-        <v>164.3525496506081</v>
+        <v>164.4325496506081</v>
       </c>
       <c r="U28" t="n">
-        <v>332.7275321249604</v>
+        <v>332.8075321249603</v>
       </c>
       <c r="V28" t="n">
-        <v>453.3389250109063</v>
+        <v>453.4189250109063</v>
       </c>
       <c r="W28" t="n">
-        <v>547.0198432705838</v>
+        <v>547.0998432705837</v>
       </c>
       <c r="X28" t="n">
-        <v>619.8406342947774</v>
+        <v>619.9206342947773</v>
       </c>
       <c r="Y28" t="n">
-        <v>653.0399349738096</v>
+        <v>653.1199349738096</v>
       </c>
     </row>
     <row r="29">
@@ -6430,76 +6430,76 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>596.4384060421568</v>
+        <v>597.4524900262056</v>
       </c>
       <c r="C29" t="n">
-        <v>466.6661047866073</v>
+        <v>467.6801887706562</v>
       </c>
       <c r="D29" t="n">
-        <v>376.4245333322136</v>
+        <v>377.4386173162624</v>
       </c>
       <c r="E29" t="n">
-        <v>292.2191902949725</v>
+        <v>293.2332742790214</v>
       </c>
       <c r="F29" t="n">
-        <v>207.482191600011</v>
+        <v>207.562191600011</v>
       </c>
       <c r="G29" t="n">
-        <v>125.2979517892592</v>
+        <v>125.3779517892592</v>
       </c>
       <c r="H29" t="n">
-        <v>51.84</v>
+        <v>51.92</v>
       </c>
       <c r="I29" t="n">
-        <v>51.84</v>
+        <v>51.92</v>
       </c>
       <c r="J29" t="n">
-        <v>134.360205073642</v>
+        <v>560.4418942939371</v>
       </c>
       <c r="K29" t="n">
-        <v>775.8802050736419</v>
+        <v>736.1134691180577</v>
       </c>
       <c r="L29" t="n">
-        <v>1417.400205073642</v>
+        <v>1378.623469118058</v>
       </c>
       <c r="M29" t="n">
-        <v>2058.920205073642</v>
+        <v>1646.814971748371</v>
       </c>
       <c r="N29" t="n">
-        <v>2230.549243836214</v>
+        <v>1646.814971748371</v>
       </c>
       <c r="O29" t="n">
-        <v>2393.691050093541</v>
+        <v>1809.956778005698</v>
       </c>
       <c r="P29" t="n">
-        <v>2592</v>
+        <v>2008.265727912157</v>
       </c>
       <c r="Q29" t="n">
-        <v>2592</v>
+        <v>2596</v>
       </c>
       <c r="R29" t="n">
-        <v>2592</v>
+        <v>2596</v>
       </c>
       <c r="S29" t="n">
-        <v>2448.504870855986</v>
+        <v>2452.504870855986</v>
       </c>
       <c r="T29" t="n">
-        <v>2186.313881748914</v>
+        <v>2190.313881748914</v>
       </c>
       <c r="U29" t="n">
-        <v>1854.889943810872</v>
+        <v>1858.889943810872</v>
       </c>
       <c r="V29" t="n">
-        <v>1542.919212329232</v>
+        <v>1546.919212329232</v>
       </c>
       <c r="W29" t="n">
-        <v>1222.339943661608</v>
+        <v>1226.339943661608</v>
       </c>
       <c r="X29" t="n">
-        <v>948.3178896609338</v>
+        <v>952.3178896609338</v>
       </c>
       <c r="Y29" t="n">
-        <v>756.0780586682001</v>
+        <v>760.0780586682001</v>
       </c>
     </row>
     <row r="30">
@@ -6509,76 +6509,76 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>168.3033844885911</v>
+        <v>1247.529260026979</v>
       </c>
       <c r="C30" t="n">
-        <v>127.79842242241</v>
+        <v>1207.024297960798</v>
       </c>
       <c r="D30" t="n">
-        <v>100.5886376772558</v>
+        <v>855.5720889732193</v>
       </c>
       <c r="E30" t="n">
-        <v>78.69763038239455</v>
+        <v>509.4386574359337</v>
       </c>
       <c r="F30" t="n">
-        <v>59.87314317241791</v>
+        <v>166.3717459835328</v>
       </c>
       <c r="G30" t="n">
-        <v>55.83964972137068</v>
+        <v>162.3382525324856</v>
       </c>
       <c r="H30" t="n">
-        <v>51.84</v>
+        <v>158.3386028111149</v>
       </c>
       <c r="I30" t="n">
-        <v>51.84</v>
+        <v>51.92</v>
       </c>
       <c r="J30" t="n">
-        <v>245.6076497036009</v>
+        <v>245.6876497036009</v>
       </c>
       <c r="K30" t="n">
-        <v>554.1188055149654</v>
+        <v>554.1988055149654</v>
       </c>
       <c r="L30" t="n">
-        <v>985.9074996573354</v>
+        <v>985.9874996573354</v>
       </c>
       <c r="M30" t="n">
-        <v>1259.211891400195</v>
+        <v>1259.291891400195</v>
       </c>
       <c r="N30" t="n">
-        <v>1584.67128421531</v>
+        <v>1584.75128421531</v>
       </c>
       <c r="O30" t="n">
-        <v>1999.520074672614</v>
+        <v>1999.600074672614</v>
       </c>
       <c r="P30" t="n">
-        <v>2253.149505368536</v>
+        <v>2253.229505368536</v>
       </c>
       <c r="Q30" t="n">
-        <v>2174.558747796677</v>
+        <v>2174.638747796677</v>
       </c>
       <c r="R30" t="n">
-        <v>1886.389711280662</v>
+        <v>1992.888314091777</v>
       </c>
       <c r="S30" t="n">
-        <v>1753.359036645168</v>
+        <v>1859.857639456283</v>
       </c>
       <c r="T30" t="n">
-        <v>1671.187985443944</v>
+        <v>1777.686588255059</v>
       </c>
       <c r="U30" t="n">
-        <v>1591.227120811013</v>
+        <v>1697.725723622128</v>
       </c>
       <c r="V30" t="n">
-        <v>1496.771901425639</v>
+        <v>1603.270504236754</v>
       </c>
       <c r="W30" t="n">
-        <v>1384.273777274297</v>
+        <v>1490.772380085412</v>
       </c>
       <c r="X30" t="n">
-        <v>960.1700000567336</v>
+        <v>1390.911027110273</v>
       </c>
       <c r="Y30" t="n">
-        <v>556.744350798012</v>
+        <v>1311.727802093975</v>
       </c>
     </row>
     <row r="31">
@@ -6588,76 +6588,76 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>681.4588756890412</v>
+        <v>681.5388756890411</v>
       </c>
       <c r="C31" t="n">
-        <v>729.2508815074769</v>
+        <v>729.3308815074769</v>
       </c>
       <c r="D31" t="n">
-        <v>764.360025632477</v>
+        <v>764.4400256324769</v>
       </c>
       <c r="E31" t="n">
-        <v>803.97892984389</v>
+        <v>804.0589298438899</v>
       </c>
       <c r="F31" t="n">
-        <v>850.1299024358254</v>
+        <v>850.2099024358254</v>
       </c>
       <c r="G31" t="n">
-        <v>925.9459486505796</v>
+        <v>926.0259486505795</v>
       </c>
       <c r="H31" t="n">
-        <v>1022.760277088666</v>
+        <v>1022.840277088666</v>
       </c>
       <c r="I31" t="n">
-        <v>1184.312618975568</v>
+        <v>1184.392618975568</v>
       </c>
       <c r="J31" t="n">
-        <v>1510.983618808348</v>
+        <v>1511.063618808347</v>
       </c>
       <c r="K31" t="n">
-        <v>1615.110403564888</v>
+        <v>1615.190403564888</v>
       </c>
       <c r="L31" t="n">
-        <v>1605.496770221213</v>
+        <v>1605.576770221213</v>
       </c>
       <c r="M31" t="n">
-        <v>1502.926687499644</v>
+        <v>1503.006687499644</v>
       </c>
       <c r="N31" t="n">
-        <v>1346.936646241608</v>
+        <v>1347.016646241608</v>
       </c>
       <c r="O31" t="n">
-        <v>1113.602925280855</v>
+        <v>1113.682925280855</v>
       </c>
       <c r="P31" t="n">
-        <v>819.8981109568782</v>
+        <v>819.9781109568783</v>
       </c>
       <c r="Q31" t="n">
-        <v>463.8958216380924</v>
+        <v>463.9758216380924</v>
       </c>
       <c r="R31" t="n">
-        <v>82.61634147829413</v>
+        <v>82.69634147829413</v>
       </c>
       <c r="S31" t="n">
-        <v>51.84</v>
+        <v>51.92</v>
       </c>
       <c r="T31" t="n">
-        <v>164.3525496506081</v>
+        <v>164.4325496506081</v>
       </c>
       <c r="U31" t="n">
-        <v>327.5991351738998</v>
+        <v>327.6791351738997</v>
       </c>
       <c r="V31" t="n">
-        <v>448.2105280598458</v>
+        <v>448.2905280598457</v>
       </c>
       <c r="W31" t="n">
-        <v>541.8914463195232</v>
+        <v>541.9714463195231</v>
       </c>
       <c r="X31" t="n">
-        <v>614.7122373437168</v>
+        <v>614.7922373437167</v>
       </c>
       <c r="Y31" t="n">
-        <v>647.911538022749</v>
+        <v>647.991538022749</v>
       </c>
     </row>
     <row r="32">
@@ -6667,76 +6667,76 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>593.4524900262056</v>
+        <v>596.5184060421568</v>
       </c>
       <c r="C32" t="n">
-        <v>463.6801887706562</v>
+        <v>466.7461047866074</v>
       </c>
       <c r="D32" t="n">
-        <v>373.4386173162624</v>
+        <v>376.5045333322136</v>
       </c>
       <c r="E32" t="n">
-        <v>289.2332742790214</v>
+        <v>292.2991902949726</v>
       </c>
       <c r="F32" t="n">
-        <v>204.4962755840599</v>
+        <v>207.5621916000111</v>
       </c>
       <c r="G32" t="n">
-        <v>122.3120357733081</v>
+        <v>125.3779517892592</v>
       </c>
       <c r="H32" t="n">
-        <v>51.84</v>
+        <v>51.92</v>
       </c>
       <c r="I32" t="n">
-        <v>51.84</v>
+        <v>51.92</v>
       </c>
       <c r="J32" t="n">
-        <v>134.360205073642</v>
+        <v>134.440205073642</v>
       </c>
       <c r="K32" t="n">
-        <v>775.8802050736419</v>
+        <v>731.5931213236511</v>
       </c>
       <c r="L32" t="n">
-        <v>1417.400205073642</v>
+        <v>949.5292438362139</v>
       </c>
       <c r="M32" t="n">
-        <v>1589.029243836214</v>
+        <v>1592.039243836214</v>
       </c>
       <c r="N32" t="n">
-        <v>2230.549243836214</v>
+        <v>2234.549243836214</v>
       </c>
       <c r="O32" t="n">
-        <v>2393.691050093541</v>
+        <v>2397.691050093541</v>
       </c>
       <c r="P32" t="n">
-        <v>2592</v>
+        <v>2596</v>
       </c>
       <c r="Q32" t="n">
-        <v>2592</v>
+        <v>2596</v>
       </c>
       <c r="R32" t="n">
-        <v>2592</v>
+        <v>2595.065916015951</v>
       </c>
       <c r="S32" t="n">
-        <v>2448.504870855986</v>
+        <v>2451.570786871937</v>
       </c>
       <c r="T32" t="n">
-        <v>2186.313881748914</v>
+        <v>2189.379797764865</v>
       </c>
       <c r="U32" t="n">
-        <v>1854.889943810872</v>
+        <v>1857.955859826824</v>
       </c>
       <c r="V32" t="n">
-        <v>1542.919212329232</v>
+        <v>1545.985128345183</v>
       </c>
       <c r="W32" t="n">
-        <v>1222.339943661608</v>
+        <v>1225.405859677559</v>
       </c>
       <c r="X32" t="n">
-        <v>948.3178896609338</v>
+        <v>951.383805676885</v>
       </c>
       <c r="Y32" t="n">
-        <v>756.0780586682001</v>
+        <v>759.1439746841513</v>
       </c>
     </row>
     <row r="33">
@@ -6746,76 +6746,76 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1001.797593356413</v>
+        <v>923.2868357845546</v>
       </c>
       <c r="C33" t="n">
-        <v>961.2926312902321</v>
+        <v>882.7818737183735</v>
       </c>
       <c r="D33" t="n">
-        <v>749.0734861621042</v>
+        <v>855.5720889732194</v>
       </c>
       <c r="E33" t="n">
-        <v>402.9400546248188</v>
+        <v>509.4386574359339</v>
       </c>
       <c r="F33" t="n">
-        <v>59.87314317241791</v>
+        <v>166.3717459835329</v>
       </c>
       <c r="G33" t="n">
-        <v>55.83964972137068</v>
+        <v>55.91964972137069</v>
       </c>
       <c r="H33" t="n">
-        <v>51.84</v>
+        <v>51.92</v>
       </c>
       <c r="I33" t="n">
-        <v>51.84</v>
+        <v>51.92</v>
       </c>
       <c r="J33" t="n">
-        <v>245.6076497036009</v>
+        <v>245.6876497036009</v>
       </c>
       <c r="K33" t="n">
-        <v>554.1188055149654</v>
+        <v>554.1988055149654</v>
       </c>
       <c r="L33" t="n">
-        <v>985.9074996573354</v>
+        <v>985.9874996573354</v>
       </c>
       <c r="M33" t="n">
-        <v>1259.211891400195</v>
+        <v>1259.291891400195</v>
       </c>
       <c r="N33" t="n">
-        <v>1584.67128421531</v>
+        <v>1584.75128421531</v>
       </c>
       <c r="O33" t="n">
-        <v>1999.520074672614</v>
+        <v>1999.600074672614</v>
       </c>
       <c r="P33" t="n">
-        <v>2253.149505368536</v>
+        <v>2253.229505368536</v>
       </c>
       <c r="Q33" t="n">
-        <v>2253.149505368536</v>
+        <v>2174.638747796677</v>
       </c>
       <c r="R33" t="n">
-        <v>2071.399071663636</v>
+        <v>1992.888314091777</v>
       </c>
       <c r="S33" t="n">
-        <v>1938.368397028141</v>
+        <v>1859.857639456283</v>
       </c>
       <c r="T33" t="n">
-        <v>1856.197345826917</v>
+        <v>1777.686588255059</v>
       </c>
       <c r="U33" t="n">
-        <v>1776.236481193986</v>
+        <v>1697.725723622128</v>
       </c>
       <c r="V33" t="n">
-        <v>1681.781261808612</v>
+        <v>1603.270504236754</v>
       </c>
       <c r="W33" t="n">
-        <v>1569.28313765727</v>
+        <v>1166.529955842987</v>
       </c>
       <c r="X33" t="n">
-        <v>1145.179360439707</v>
+        <v>1066.668602867848</v>
       </c>
       <c r="Y33" t="n">
-        <v>1065.99613542341</v>
+        <v>987.4853778515511</v>
       </c>
     </row>
     <row r="34">
@@ -6825,76 +6825,76 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>681.4588756890412</v>
+        <v>686.6672726401017</v>
       </c>
       <c r="C34" t="n">
-        <v>729.2508815074769</v>
+        <v>734.4592784585375</v>
       </c>
       <c r="D34" t="n">
-        <v>764.360025632477</v>
+        <v>769.5684225835375</v>
       </c>
       <c r="E34" t="n">
-        <v>803.97892984389</v>
+        <v>809.1873267949505</v>
       </c>
       <c r="F34" t="n">
-        <v>850.1299024358254</v>
+        <v>855.338299386886</v>
       </c>
       <c r="G34" t="n">
-        <v>925.9459486505796</v>
+        <v>931.1543456016401</v>
       </c>
       <c r="H34" t="n">
-        <v>1022.760277088666</v>
+        <v>1027.968674039726</v>
       </c>
       <c r="I34" t="n">
-        <v>1184.312618975568</v>
+        <v>1189.521015926629</v>
       </c>
       <c r="J34" t="n">
-        <v>1510.983618808348</v>
+        <v>1516.192015759408</v>
       </c>
       <c r="K34" t="n">
-        <v>1615.110403564888</v>
+        <v>1615.190403564888</v>
       </c>
       <c r="L34" t="n">
-        <v>1605.496770221213</v>
+        <v>1605.576770221213</v>
       </c>
       <c r="M34" t="n">
-        <v>1502.926687499644</v>
+        <v>1503.006687499644</v>
       </c>
       <c r="N34" t="n">
-        <v>1346.936646241608</v>
+        <v>1347.016646241608</v>
       </c>
       <c r="O34" t="n">
-        <v>1113.602925280855</v>
+        <v>1113.682925280855</v>
       </c>
       <c r="P34" t="n">
-        <v>819.8981109568782</v>
+        <v>819.9781109568783</v>
       </c>
       <c r="Q34" t="n">
-        <v>463.8958216380924</v>
+        <v>463.9758216380924</v>
       </c>
       <c r="R34" t="n">
-        <v>82.61634147829413</v>
+        <v>82.69634147829412</v>
       </c>
       <c r="S34" t="n">
-        <v>51.84</v>
+        <v>51.92</v>
       </c>
       <c r="T34" t="n">
-        <v>164.3525496506081</v>
+        <v>164.4325496506081</v>
       </c>
       <c r="U34" t="n">
-        <v>332.7275321249604</v>
+        <v>332.8075321249603</v>
       </c>
       <c r="V34" t="n">
-        <v>453.3389250109063</v>
+        <v>453.4189250109063</v>
       </c>
       <c r="W34" t="n">
-        <v>547.0198432705838</v>
+        <v>547.0998432705837</v>
       </c>
       <c r="X34" t="n">
-        <v>614.7122373437168</v>
+        <v>619.9206342947773</v>
       </c>
       <c r="Y34" t="n">
-        <v>647.911538022749</v>
+        <v>653.1199349738096</v>
       </c>
     </row>
     <row r="35">
@@ -6904,76 +6904,76 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>444.0238605876121</v>
+        <v>444.0238605876112</v>
       </c>
       <c r="C35" t="n">
-        <v>338.493983574487</v>
+        <v>338.4939835744861</v>
       </c>
       <c r="D35" t="n">
-        <v>272.4948363625175</v>
+        <v>272.4948363625166</v>
       </c>
       <c r="E35" t="n">
-        <v>212.5319175677007</v>
+        <v>212.5319175676998</v>
       </c>
       <c r="F35" t="n">
-        <v>152.0373431151635</v>
+        <v>152.0373431151626</v>
       </c>
       <c r="G35" t="n">
-        <v>94.09552754683585</v>
+        <v>94.09552754683496</v>
       </c>
       <c r="H35" t="n">
-        <v>44.88000000000088</v>
+        <v>44.88</v>
       </c>
       <c r="I35" t="n">
-        <v>44.88000000000088</v>
+        <v>44.88</v>
       </c>
       <c r="J35" t="n">
-        <v>553.401894293938</v>
+        <v>127.400205073642</v>
       </c>
       <c r="K35" t="n">
-        <v>1108.791894293949</v>
+        <v>303.0717798977627</v>
       </c>
       <c r="L35" t="n">
-        <v>1326.728016806512</v>
+        <v>771.7692438362141</v>
       </c>
       <c r="M35" t="n">
-        <v>1882.118016806514</v>
+        <v>1327.159243836214</v>
       </c>
       <c r="N35" t="n">
-        <v>1882.549243836251</v>
+        <v>1882.549243836214</v>
       </c>
       <c r="O35" t="n">
-        <v>2045.691050093578</v>
+        <v>2045.691050093541</v>
       </c>
       <c r="P35" t="n">
-        <v>2244.000000000037</v>
+        <v>2244</v>
       </c>
       <c r="Q35" t="n">
-        <v>2244.000000000037</v>
+        <v>2244</v>
       </c>
       <c r="R35" t="n">
-        <v>2244.000000000037</v>
+        <v>2244</v>
       </c>
       <c r="S35" t="n">
-        <v>2124.747295098447</v>
+        <v>2124.74729509841</v>
       </c>
       <c r="T35" t="n">
-        <v>1886.798730233799</v>
+        <v>1886.798730233762</v>
       </c>
       <c r="U35" t="n">
-        <v>1579.617216538182</v>
+        <v>1579.617216538145</v>
       </c>
       <c r="V35" t="n">
-        <v>1291.888909298966</v>
+        <v>1291.888909298929</v>
       </c>
       <c r="W35" t="n">
-        <v>1000.184041495742</v>
+        <v>995.5520648737293</v>
       </c>
       <c r="X35" t="n">
-        <v>750.404411737492</v>
+        <v>745.7724351154791</v>
       </c>
       <c r="Y35" t="n">
-        <v>582.4070049871824</v>
+        <v>577.7750283651696</v>
       </c>
     </row>
     <row r="36">
@@ -6983,76 +6983,76 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>759.5118758706012</v>
+        <v>412.5947468113353</v>
       </c>
       <c r="C36" t="n">
-        <v>743.2493380468444</v>
+        <v>47.84736050272993</v>
       </c>
       <c r="D36" t="n">
-        <v>391.797129059266</v>
+        <v>44.88</v>
       </c>
       <c r="E36" t="n">
-        <v>238.2423680625408</v>
+        <v>44.88</v>
       </c>
       <c r="F36" t="n">
-        <v>238.2423680625408</v>
+        <v>44.88</v>
       </c>
       <c r="G36" t="n">
-        <v>238.2423680625408</v>
+        <v>44.88</v>
       </c>
       <c r="H36" t="n">
-        <v>238.2423680625408</v>
+        <v>44.88</v>
       </c>
       <c r="I36" t="n">
-        <v>44.88000000000088</v>
+        <v>44.88</v>
       </c>
       <c r="J36" t="n">
-        <v>238.6476497036017</v>
+        <v>238.6476497036008</v>
       </c>
       <c r="K36" t="n">
-        <v>547.1588055149663</v>
+        <v>547.1588055149654</v>
       </c>
       <c r="L36" t="n">
-        <v>976.7579942888365</v>
+        <v>978.9474996573354</v>
       </c>
       <c r="M36" t="n">
-        <v>1250.062386031696</v>
+        <v>1252.251891400195</v>
       </c>
       <c r="N36" t="n">
-        <v>1575.521778846811</v>
+        <v>1575.521778846855</v>
       </c>
       <c r="O36" t="n">
-        <v>1990.370569304115</v>
+        <v>1990.370569304159</v>
       </c>
       <c r="P36" t="n">
-        <v>2244.000000000037</v>
+        <v>2244.00000000008</v>
       </c>
       <c r="Q36" t="n">
-        <v>2165.409242428178</v>
+        <v>2166.976961853761</v>
       </c>
       <c r="R36" t="n">
-        <v>1659.416384480854</v>
+        <v>2009.468952391285</v>
       </c>
       <c r="S36" t="n">
-        <v>1550.628134087784</v>
+        <v>1900.680701998215</v>
       </c>
       <c r="T36" t="n">
-        <v>1492.699507128984</v>
+        <v>1842.752075039415</v>
       </c>
       <c r="U36" t="n">
-        <v>1436.981066738477</v>
+        <v>1787.033634648908</v>
       </c>
       <c r="V36" t="n">
-        <v>1366.768271595527</v>
+        <v>1716.820839505958</v>
       </c>
       <c r="W36" t="n">
-        <v>930.0277232017613</v>
+        <v>1628.565139597041</v>
       </c>
       <c r="X36" t="n">
-        <v>854.4087944690466</v>
+        <v>1204.461362379478</v>
       </c>
       <c r="Y36" t="n">
-        <v>799.4679936951735</v>
+        <v>801.0357131207561</v>
       </c>
     </row>
     <row r="37">
@@ -7062,76 +7062,76 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>608.5605946885332</v>
+        <v>608.5605946885323</v>
       </c>
       <c r="C37" t="n">
-        <v>680.112600506969</v>
+        <v>680.1126005069681</v>
       </c>
       <c r="D37" t="n">
-        <v>738.981744631969</v>
+        <v>738.9817446319681</v>
       </c>
       <c r="E37" t="n">
-        <v>802.360648843382</v>
+        <v>802.3606488433811</v>
       </c>
       <c r="F37" t="n">
-        <v>872.2716214353176</v>
+        <v>872.2716214353167</v>
       </c>
       <c r="G37" t="n">
-        <v>971.8476676500717</v>
+        <v>971.8476676500708</v>
       </c>
       <c r="H37" t="n">
-        <v>1092.421996088158</v>
+        <v>1092.421996088157</v>
       </c>
       <c r="I37" t="n">
-        <v>1277.73433797506</v>
+        <v>1277.734337975059</v>
       </c>
       <c r="J37" t="n">
-        <v>1286.61533780784</v>
+        <v>1286.615337807839</v>
       </c>
       <c r="K37" t="n">
-        <v>1414.50212256438</v>
+        <v>1414.502122564379</v>
       </c>
       <c r="L37" t="n">
-        <v>1428.839800524244</v>
+        <v>1428.839800524243</v>
       </c>
       <c r="M37" t="n">
-        <v>1350.512142045099</v>
+        <v>1350.512142045098</v>
       </c>
       <c r="N37" t="n">
-        <v>1218.764525029488</v>
+        <v>1218.764525029487</v>
       </c>
       <c r="O37" t="n">
         <v>1009.673228311158</v>
       </c>
       <c r="P37" t="n">
-        <v>740.2108382296065</v>
+        <v>740.2108382296055</v>
       </c>
       <c r="Q37" t="n">
-        <v>408.4509731532448</v>
+        <v>408.4509731532439</v>
       </c>
       <c r="R37" t="n">
-        <v>51.41391723587076</v>
+        <v>51.41391723586989</v>
       </c>
       <c r="S37" t="n">
-        <v>44.88000000000088</v>
+        <v>44.88</v>
       </c>
       <c r="T37" t="n">
-        <v>44.88000000000088</v>
+        <v>44.88</v>
       </c>
       <c r="U37" t="n">
-        <v>135.900854173392</v>
+        <v>135.9008541733911</v>
       </c>
       <c r="V37" t="n">
-        <v>280.2722470593379</v>
+        <v>280.272247059337</v>
       </c>
       <c r="W37" t="n">
-        <v>397.7131653190153</v>
+        <v>397.7131653190144</v>
       </c>
       <c r="X37" t="n">
-        <v>494.2939563432088</v>
+        <v>494.2939563432079</v>
       </c>
       <c r="Y37" t="n">
-        <v>551.2532570222411</v>
+        <v>551.2532570222402</v>
       </c>
     </row>
     <row r="38">
@@ -7141,76 +7141,76 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>444.0238605876121</v>
+        <v>439.3918839656726</v>
       </c>
       <c r="C38" t="n">
-        <v>338.493983574487</v>
+        <v>333.8620069525474</v>
       </c>
       <c r="D38" t="n">
-        <v>272.4948363625175</v>
+        <v>267.8628597405779</v>
       </c>
       <c r="E38" t="n">
-        <v>212.5319175677007</v>
+        <v>207.8999409457611</v>
       </c>
       <c r="F38" t="n">
-        <v>152.0373431151635</v>
+        <v>147.4053664932239</v>
       </c>
       <c r="G38" t="n">
-        <v>94.09552754683585</v>
+        <v>89.46355092489623</v>
       </c>
       <c r="H38" t="n">
-        <v>44.88000000000088</v>
+        <v>44.88</v>
       </c>
       <c r="I38" t="n">
-        <v>44.88000000000088</v>
+        <v>44.88</v>
       </c>
       <c r="J38" t="n">
-        <v>553.401894293938</v>
+        <v>553.4018942939372</v>
       </c>
       <c r="K38" t="n">
-        <v>729.0734691180586</v>
+        <v>729.0734691180577</v>
       </c>
       <c r="L38" t="n">
-        <v>947.0095916306215</v>
+        <v>947.0095916306205</v>
       </c>
       <c r="M38" t="n">
-        <v>947.0095916306216</v>
+        <v>1327.159243836214</v>
       </c>
       <c r="N38" t="n">
-        <v>970.0781937427171</v>
+        <v>1327.159243836214</v>
       </c>
       <c r="O38" t="n">
-        <v>1133.220000000044</v>
+        <v>1490.301050093541</v>
       </c>
       <c r="P38" t="n">
-        <v>1688.610000000044</v>
+        <v>1688.61</v>
       </c>
       <c r="Q38" t="n">
-        <v>2244.000000000044</v>
+        <v>2244</v>
       </c>
       <c r="R38" t="n">
-        <v>2244.000000000044</v>
+        <v>2244.000000000073</v>
       </c>
       <c r="S38" t="n">
-        <v>2124.747295098454</v>
+        <v>2124.747295098483</v>
       </c>
       <c r="T38" t="n">
-        <v>1886.798730233806</v>
+        <v>1886.798730233835</v>
       </c>
       <c r="U38" t="n">
-        <v>1579.617216538189</v>
+        <v>1579.617216538218</v>
       </c>
       <c r="V38" t="n">
-        <v>1291.888909298973</v>
+        <v>1291.888909299002</v>
       </c>
       <c r="W38" t="n">
-        <v>995.5520648737734</v>
+        <v>995.5520648738025</v>
       </c>
       <c r="X38" t="n">
-        <v>745.7724351155232</v>
+        <v>745.7724351155523</v>
       </c>
       <c r="Y38" t="n">
-        <v>577.7750283652138</v>
+        <v>577.7750283652429</v>
       </c>
     </row>
     <row r="39">
@@ -7220,76 +7220,76 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1456.481572840305</v>
+        <v>1450.27993828587</v>
       </c>
       <c r="C39" t="n">
-        <v>1091.7341865317</v>
+        <v>1085.532551977265</v>
       </c>
       <c r="D39" t="n">
-        <v>1088.76682602897</v>
+        <v>734.0803429896864</v>
       </c>
       <c r="E39" t="n">
-        <v>742.6333944916846</v>
+        <v>387.9469114524009</v>
       </c>
       <c r="F39" t="n">
-        <v>399.5664830392837</v>
+        <v>44.88</v>
       </c>
       <c r="G39" t="n">
-        <v>399.5664830392837</v>
+        <v>44.88</v>
       </c>
       <c r="H39" t="n">
-        <v>238.2423680625408</v>
+        <v>44.88</v>
       </c>
       <c r="I39" t="n">
-        <v>44.88000000000088</v>
+        <v>44.88</v>
       </c>
       <c r="J39" t="n">
-        <v>238.6476497036017</v>
+        <v>238.6476497036008</v>
       </c>
       <c r="K39" t="n">
-        <v>547.1588055149663</v>
+        <v>547.1588055149654</v>
       </c>
       <c r="L39" t="n">
-        <v>978.9474996573363</v>
+        <v>976.7579942888729</v>
       </c>
       <c r="M39" t="n">
-        <v>1252.251891400196</v>
+        <v>1250.062386031732</v>
       </c>
       <c r="N39" t="n">
-        <v>1575.521778846819</v>
+        <v>1575.521778846848</v>
       </c>
       <c r="O39" t="n">
-        <v>1990.370569304122</v>
+        <v>1990.370569304152</v>
       </c>
       <c r="P39" t="n">
-        <v>2244.000000000044</v>
+        <v>2244.000000000073</v>
       </c>
       <c r="Q39" t="n">
-        <v>2165.409242428186</v>
+        <v>2244.000000000073</v>
       </c>
       <c r="R39" t="n">
-        <v>2007.90123296571</v>
+        <v>2086.491990537597</v>
       </c>
       <c r="S39" t="n">
-        <v>1899.11298257264</v>
+        <v>1977.703740144527</v>
       </c>
       <c r="T39" t="n">
-        <v>1841.18435561384</v>
+        <v>1919.775113185727</v>
       </c>
       <c r="U39" t="n">
-        <v>1785.465915223333</v>
+        <v>1864.05667279522</v>
       </c>
       <c r="V39" t="n">
-        <v>1715.253120080383</v>
+        <v>1793.843877652271</v>
       </c>
       <c r="W39" t="n">
-        <v>1626.997420171466</v>
+        <v>1705.588177743353</v>
       </c>
       <c r="X39" t="n">
-        <v>1551.378491438751</v>
+        <v>1629.969249010638</v>
       </c>
       <c r="Y39" t="n">
-        <v>1496.437690664878</v>
+        <v>1575.028448236765</v>
       </c>
     </row>
     <row r="40">
@@ -7299,76 +7299,76 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>644.6165790751243</v>
+        <v>788.9879719610695</v>
       </c>
       <c r="C40" t="n">
-        <v>716.16858489356</v>
+        <v>788.9879719610695</v>
       </c>
       <c r="D40" t="n">
-        <v>716.16858489356</v>
+        <v>847.8571160860696</v>
       </c>
       <c r="E40" t="n">
-        <v>779.547489104973</v>
+        <v>847.8571160860696</v>
       </c>
       <c r="F40" t="n">
-        <v>849.4584616969084</v>
+        <v>917.7680886780051</v>
       </c>
       <c r="G40" t="n">
-        <v>949.0345079116626</v>
+        <v>1017.344134892759</v>
       </c>
       <c r="H40" t="n">
-        <v>1069.608836349749</v>
+        <v>1137.918463330845</v>
       </c>
       <c r="I40" t="n">
-        <v>1069.608836349749</v>
+        <v>1323.230805217748</v>
       </c>
       <c r="J40" t="n">
-        <v>1420.039836182528</v>
+        <v>1332.111805050527</v>
       </c>
       <c r="K40" t="n">
-        <v>1428.839800524244</v>
+        <v>1428.839800524243</v>
       </c>
       <c r="L40" t="n">
-        <v>1428.839800524244</v>
+        <v>1428.839800524243</v>
       </c>
       <c r="M40" t="n">
-        <v>1350.512142045099</v>
+        <v>1350.512142045098</v>
       </c>
       <c r="N40" t="n">
-        <v>1218.764525029488</v>
+        <v>1218.764525029487</v>
       </c>
       <c r="O40" t="n">
         <v>1009.673228311158</v>
       </c>
       <c r="P40" t="n">
-        <v>740.2108382296065</v>
+        <v>740.2108382296055</v>
       </c>
       <c r="Q40" t="n">
-        <v>408.4509731532448</v>
+        <v>408.4509731532439</v>
       </c>
       <c r="R40" t="n">
-        <v>51.41391723587076</v>
+        <v>51.41391723586987</v>
       </c>
       <c r="S40" t="n">
-        <v>44.88000000000088</v>
+        <v>44.88</v>
       </c>
       <c r="T40" t="n">
-        <v>181.152549650609</v>
+        <v>181.1525496506081</v>
       </c>
       <c r="U40" t="n">
-        <v>373.2875321249612</v>
+        <v>373.2875321249604</v>
       </c>
       <c r="V40" t="n">
-        <v>373.2875321249612</v>
+        <v>517.6589250109064</v>
       </c>
       <c r="W40" t="n">
-        <v>490.7284503846386</v>
+        <v>635.0998432705838</v>
       </c>
       <c r="X40" t="n">
-        <v>587.3092414088321</v>
+        <v>731.6806342947774</v>
       </c>
       <c r="Y40" t="n">
-        <v>587.3092414088321</v>
+        <v>731.6806342947774</v>
       </c>
     </row>
     <row r="41">
@@ -7378,76 +7378,76 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>444.0238605876121</v>
+        <v>444.0238605876112</v>
       </c>
       <c r="C41" t="n">
-        <v>338.493983574487</v>
+        <v>338.4939835744861</v>
       </c>
       <c r="D41" t="n">
-        <v>272.4948363625175</v>
+        <v>272.4948363625166</v>
       </c>
       <c r="E41" t="n">
-        <v>212.5319175677007</v>
+        <v>212.5319175676998</v>
       </c>
       <c r="F41" t="n">
-        <v>152.0373431151635</v>
+        <v>152.0373431151626</v>
       </c>
       <c r="G41" t="n">
-        <v>94.09552754683585</v>
+        <v>94.09552754683496</v>
       </c>
       <c r="H41" t="n">
-        <v>44.88000000000088</v>
+        <v>44.88</v>
       </c>
       <c r="I41" t="n">
-        <v>44.88000000000088</v>
+        <v>44.88</v>
       </c>
       <c r="J41" t="n">
-        <v>553.401894293938</v>
+        <v>127.400205073642</v>
       </c>
       <c r="K41" t="n">
-        <v>729.0734691180586</v>
+        <v>303.0717798977627</v>
       </c>
       <c r="L41" t="n">
-        <v>947.0095916306215</v>
+        <v>771.7692438362141</v>
       </c>
       <c r="M41" t="n">
-        <v>1327.159243836256</v>
+        <v>1327.159243836214</v>
       </c>
       <c r="N41" t="n">
-        <v>1327.159243836256</v>
+        <v>1882.549243836214</v>
       </c>
       <c r="O41" t="n">
-        <v>1490.301050093583</v>
+        <v>2045.691050093541</v>
       </c>
       <c r="P41" t="n">
-        <v>1688.610000000042</v>
+        <v>2244</v>
       </c>
       <c r="Q41" t="n">
-        <v>2244.000000000044</v>
+        <v>2244</v>
       </c>
       <c r="R41" t="n">
-        <v>2244.000000000044</v>
+        <v>2244</v>
       </c>
       <c r="S41" t="n">
-        <v>2124.747295098454</v>
+        <v>2124.74729509841</v>
       </c>
       <c r="T41" t="n">
-        <v>1886.798730233806</v>
+        <v>1886.798730233762</v>
       </c>
       <c r="U41" t="n">
-        <v>1579.617216538189</v>
+        <v>1579.617216538145</v>
       </c>
       <c r="V41" t="n">
-        <v>1291.888909298973</v>
+        <v>1291.888909298929</v>
       </c>
       <c r="W41" t="n">
-        <v>995.5520648737734</v>
+        <v>995.5520648737293</v>
       </c>
       <c r="X41" t="n">
-        <v>745.7724351155232</v>
+        <v>745.7724351154791</v>
       </c>
       <c r="Y41" t="n">
-        <v>577.7750283652138</v>
+        <v>577.7750283651696</v>
       </c>
     </row>
     <row r="42">
@@ -7457,76 +7457,76 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>64.10989832648768</v>
+        <v>1107.996724355486</v>
       </c>
       <c r="C42" t="n">
-        <v>47.84736050273082</v>
+        <v>1091.734186531729</v>
       </c>
       <c r="D42" t="n">
-        <v>44.88000000000088</v>
+        <v>1088.766826028999</v>
       </c>
       <c r="E42" t="n">
-        <v>44.88000000000088</v>
+        <v>742.6333944917137</v>
       </c>
       <c r="F42" t="n">
-        <v>44.88000000000088</v>
+        <v>742.6333944917137</v>
       </c>
       <c r="G42" t="n">
-        <v>44.88000000000088</v>
+        <v>566.4844420263349</v>
       </c>
       <c r="H42" t="n">
-        <v>44.88000000000088</v>
+        <v>238.24236806254</v>
       </c>
       <c r="I42" t="n">
-        <v>44.88000000000088</v>
+        <v>44.88</v>
       </c>
       <c r="J42" t="n">
-        <v>238.6476497036017</v>
+        <v>238.6476497036008</v>
       </c>
       <c r="K42" t="n">
-        <v>547.1588055149663</v>
+        <v>547.1588055149654</v>
       </c>
       <c r="L42" t="n">
-        <v>978.9474996573363</v>
+        <v>978.9474996573354</v>
       </c>
       <c r="M42" t="n">
-        <v>1252.251891400196</v>
+        <v>1252.251891400195</v>
       </c>
       <c r="N42" t="n">
-        <v>1575.521778846826</v>
+        <v>1575.521778846848</v>
       </c>
       <c r="O42" t="n">
-        <v>1990.37056930413</v>
+        <v>1990.370569304152</v>
       </c>
       <c r="P42" t="n">
-        <v>2244.000000000051</v>
+        <v>2244.000000000073</v>
       </c>
       <c r="Q42" t="n">
-        <v>2166.976961853762</v>
+        <v>2165.409242428215</v>
       </c>
       <c r="R42" t="n">
-        <v>1660.984103906438</v>
+        <v>2007.901232965739</v>
       </c>
       <c r="S42" t="n">
-        <v>1203.711005028519</v>
+        <v>1899.112982572669</v>
       </c>
       <c r="T42" t="n">
-        <v>797.2975295848705</v>
+        <v>1841.184355613869</v>
       </c>
       <c r="U42" t="n">
-        <v>741.5790891943636</v>
+        <v>1785.465915223362</v>
       </c>
       <c r="V42" t="n">
-        <v>671.366294051414</v>
+        <v>1715.253120080412</v>
       </c>
       <c r="W42" t="n">
-        <v>583.1105941424963</v>
+        <v>1278.512571686646</v>
       </c>
       <c r="X42" t="n">
-        <v>159.0068169249331</v>
+        <v>1202.893642953931</v>
       </c>
       <c r="Y42" t="n">
-        <v>104.06601615106</v>
+        <v>1147.952842180058</v>
       </c>
     </row>
     <row r="43">
@@ -7536,76 +7536,76 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>653.8122901657503</v>
+        <v>430.5948697912525</v>
       </c>
       <c r="C43" t="n">
-        <v>725.364295984186</v>
+        <v>430.5948697912525</v>
       </c>
       <c r="D43" t="n">
-        <v>784.2334401091861</v>
+        <v>430.5948697912525</v>
       </c>
       <c r="E43" t="n">
-        <v>847.612344320599</v>
+        <v>475.1483268032452</v>
       </c>
       <c r="F43" t="n">
-        <v>917.5233169125345</v>
+        <v>545.0592993951807</v>
       </c>
       <c r="G43" t="n">
-        <v>1017.099363127289</v>
+        <v>644.6353456099348</v>
       </c>
       <c r="H43" t="n">
-        <v>1137.673691565375</v>
+        <v>765.2096740480209</v>
       </c>
       <c r="I43" t="n">
-        <v>1322.986033452277</v>
+        <v>950.5220159349235</v>
       </c>
       <c r="J43" t="n">
-        <v>1331.867033285057</v>
+        <v>1300.953015767703</v>
       </c>
       <c r="K43" t="n">
-        <v>1428.839800524244</v>
+        <v>1428.839800524243</v>
       </c>
       <c r="L43" t="n">
-        <v>1428.839800524244</v>
+        <v>1428.839800524243</v>
       </c>
       <c r="M43" t="n">
-        <v>1350.512142045099</v>
+        <v>1350.512142045098</v>
       </c>
       <c r="N43" t="n">
-        <v>1218.764525029488</v>
+        <v>1218.764525029487</v>
       </c>
       <c r="O43" t="n">
         <v>1009.673228311158</v>
       </c>
       <c r="P43" t="n">
-        <v>740.2108382296065</v>
+        <v>740.2108382296055</v>
       </c>
       <c r="Q43" t="n">
-        <v>408.4509731532448</v>
+        <v>408.4509731532439</v>
       </c>
       <c r="R43" t="n">
-        <v>51.41391723587076</v>
+        <v>51.41391723586989</v>
       </c>
       <c r="S43" t="n">
-        <v>44.88000000000088</v>
+        <v>44.88</v>
       </c>
       <c r="T43" t="n">
-        <v>181.152549650609</v>
+        <v>181.1525496506081</v>
       </c>
       <c r="U43" t="n">
-        <v>181.152549650609</v>
+        <v>373.2875321249604</v>
       </c>
       <c r="V43" t="n">
-        <v>325.523942536555</v>
+        <v>373.2875321249604</v>
       </c>
       <c r="W43" t="n">
-        <v>442.9648607962324</v>
+        <v>373.2875321249604</v>
       </c>
       <c r="X43" t="n">
-        <v>539.5456518204259</v>
+        <v>373.2875321249604</v>
       </c>
       <c r="Y43" t="n">
-        <v>596.5049524994581</v>
+        <v>373.2875321249604</v>
       </c>
     </row>
     <row r="44">
@@ -7615,76 +7615,76 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>439.3918839656435</v>
+        <v>444.0238605876114</v>
       </c>
       <c r="C44" t="n">
-        <v>333.8620069525183</v>
+        <v>338.4939835744862</v>
       </c>
       <c r="D44" t="n">
-        <v>267.8628597405488</v>
+        <v>272.4948363625167</v>
       </c>
       <c r="E44" t="n">
-        <v>207.899940945732</v>
+        <v>212.5319175676998</v>
       </c>
       <c r="F44" t="n">
-        <v>147.4053664931947</v>
+        <v>152.0373431151626</v>
       </c>
       <c r="G44" t="n">
-        <v>94.09552754683585</v>
+        <v>94.09552754683497</v>
       </c>
       <c r="H44" t="n">
-        <v>44.88000000000088</v>
+        <v>44.88</v>
       </c>
       <c r="I44" t="n">
-        <v>44.88000000000088</v>
+        <v>44.88</v>
       </c>
       <c r="J44" t="n">
-        <v>127.4002050736429</v>
+        <v>553.4018942939372</v>
       </c>
       <c r="K44" t="n">
-        <v>682.7902050736537</v>
+        <v>729.0734691180577</v>
       </c>
       <c r="L44" t="n">
-        <v>1238.180205073665</v>
+        <v>947.0095916306205</v>
       </c>
       <c r="M44" t="n">
-        <v>1238.180205073665</v>
+        <v>1502.399591630621</v>
       </c>
       <c r="N44" t="n">
-        <v>1327.159243836255</v>
+        <v>1502.399591630621</v>
       </c>
       <c r="O44" t="n">
-        <v>1490.301050093581</v>
+        <v>1665.541397887948</v>
       </c>
       <c r="P44" t="n">
-        <v>1688.61000000004</v>
+        <v>1863.850347794407</v>
       </c>
       <c r="Q44" t="n">
-        <v>2244.000000000044</v>
+        <v>2244</v>
       </c>
       <c r="R44" t="n">
-        <v>2244.000000000044</v>
+        <v>2244</v>
       </c>
       <c r="S44" t="n">
-        <v>2124.747295098454</v>
+        <v>2124.74729509841</v>
       </c>
       <c r="T44" t="n">
-        <v>1886.798730233806</v>
+        <v>1886.798730233762</v>
       </c>
       <c r="U44" t="n">
-        <v>1579.617216538189</v>
+        <v>1579.617216538145</v>
       </c>
       <c r="V44" t="n">
-        <v>1291.888909298973</v>
+        <v>1291.888909298929</v>
       </c>
       <c r="W44" t="n">
-        <v>995.5520648737734</v>
+        <v>995.5520648737293</v>
       </c>
       <c r="X44" t="n">
-        <v>745.7724351155232</v>
+        <v>745.7724351154791</v>
       </c>
       <c r="Y44" t="n">
-        <v>577.7750283652138</v>
+        <v>582.4070049871816</v>
       </c>
     </row>
     <row r="45">
@@ -7694,76 +7694,76 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>759.5118758706232</v>
+        <v>759.5118758706376</v>
       </c>
       <c r="C45" t="n">
-        <v>743.2493380468663</v>
+        <v>394.7644895620322</v>
       </c>
       <c r="D45" t="n">
-        <v>584.3757995998263</v>
+        <v>391.7971290593023</v>
       </c>
       <c r="E45" t="n">
-        <v>238.2423680625408</v>
+        <v>391.7971290593023</v>
       </c>
       <c r="F45" t="n">
-        <v>238.2423680625408</v>
+        <v>391.7971290593023</v>
       </c>
       <c r="G45" t="n">
-        <v>238.2423680625408</v>
+        <v>373.1220739637949</v>
       </c>
       <c r="H45" t="n">
-        <v>238.2423680625408</v>
+        <v>44.88</v>
       </c>
       <c r="I45" t="n">
-        <v>44.88000000000088</v>
+        <v>44.88</v>
       </c>
       <c r="J45" t="n">
-        <v>238.6476497036017</v>
+        <v>238.6476497036008</v>
       </c>
       <c r="K45" t="n">
-        <v>547.1588055149663</v>
+        <v>547.1588055149654</v>
       </c>
       <c r="L45" t="n">
-        <v>978.9474996573363</v>
+        <v>976.7579942888729</v>
       </c>
       <c r="M45" t="n">
-        <v>1252.251891400196</v>
+        <v>1250.062386031732</v>
       </c>
       <c r="N45" t="n">
-        <v>1575.521778846833</v>
+        <v>1575.521778846848</v>
       </c>
       <c r="O45" t="n">
-        <v>1990.370569304137</v>
+        <v>1990.370569304152</v>
       </c>
       <c r="P45" t="n">
-        <v>2244.000000000059</v>
+        <v>2244.000000000073</v>
       </c>
       <c r="Q45" t="n">
-        <v>2165.4092424282</v>
+        <v>2165.409242428215</v>
       </c>
       <c r="R45" t="n">
-        <v>1659.416384480876</v>
+        <v>2007.901232965739</v>
       </c>
       <c r="S45" t="n">
-        <v>1202.143285602957</v>
+        <v>1899.112982572669</v>
       </c>
       <c r="T45" t="n">
-        <v>1144.214658644157</v>
+        <v>1841.184355613869</v>
       </c>
       <c r="U45" t="n">
-        <v>1088.496218253651</v>
+        <v>1785.465915223362</v>
       </c>
       <c r="V45" t="n">
-        <v>1018.283423110701</v>
+        <v>1715.253120080412</v>
       </c>
       <c r="W45" t="n">
-        <v>930.0277232017833</v>
+        <v>1278.512571686646</v>
       </c>
       <c r="X45" t="n">
-        <v>854.4087944690685</v>
+        <v>854.408794469083</v>
       </c>
       <c r="Y45" t="n">
-        <v>799.4679936951954</v>
+        <v>799.4679936952099</v>
       </c>
     </row>
     <row r="46">
@@ -7773,76 +7773,76 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>608.5605946885332</v>
+        <v>692.407180936876</v>
       </c>
       <c r="C46" t="n">
-        <v>680.112600506969</v>
+        <v>763.9591867553117</v>
       </c>
       <c r="D46" t="n">
-        <v>738.981744631969</v>
+        <v>822.8283308803118</v>
       </c>
       <c r="E46" t="n">
-        <v>802.360648843382</v>
+        <v>822.8283308803118</v>
       </c>
       <c r="F46" t="n">
-        <v>872.2716214353176</v>
+        <v>822.8283308803118</v>
       </c>
       <c r="G46" t="n">
-        <v>971.8476676500717</v>
+        <v>822.8283308803118</v>
       </c>
       <c r="H46" t="n">
-        <v>1092.421996088158</v>
+        <v>822.8283308803118</v>
       </c>
       <c r="I46" t="n">
-        <v>1277.73433797506</v>
+        <v>1008.140672767214</v>
       </c>
       <c r="J46" t="n">
-        <v>1286.61533780784</v>
+        <v>1286.615337807839</v>
       </c>
       <c r="K46" t="n">
-        <v>1414.50212256438</v>
+        <v>1414.502122564379</v>
       </c>
       <c r="L46" t="n">
-        <v>1428.839800524244</v>
+        <v>1428.839800524243</v>
       </c>
       <c r="M46" t="n">
-        <v>1350.512142045099</v>
+        <v>1350.512142045098</v>
       </c>
       <c r="N46" t="n">
-        <v>1218.764525029488</v>
+        <v>1218.764525029487</v>
       </c>
       <c r="O46" t="n">
         <v>1009.673228311158</v>
       </c>
       <c r="P46" t="n">
-        <v>740.2108382296065</v>
+        <v>740.2108382296055</v>
       </c>
       <c r="Q46" t="n">
-        <v>408.4509731532448</v>
+        <v>408.4509731532439</v>
       </c>
       <c r="R46" t="n">
-        <v>51.41391723587076</v>
+        <v>51.41391723586987</v>
       </c>
       <c r="S46" t="n">
-        <v>44.88000000000088</v>
+        <v>44.88</v>
       </c>
       <c r="T46" t="n">
-        <v>181.152549650609</v>
+        <v>181.1525496506081</v>
       </c>
       <c r="U46" t="n">
-        <v>280.2722470593379</v>
+        <v>373.2875321249604</v>
       </c>
       <c r="V46" t="n">
-        <v>280.2722470593379</v>
+        <v>517.6589250109064</v>
       </c>
       <c r="W46" t="n">
-        <v>397.7131653190153</v>
+        <v>635.0998432705838</v>
       </c>
       <c r="X46" t="n">
-        <v>494.2939563432088</v>
+        <v>635.0998432705838</v>
       </c>
       <c r="Y46" t="n">
-        <v>551.2532570222411</v>
+        <v>635.0998432705838</v>
       </c>
     </row>
   </sheetData>
@@ -7964,7 +7964,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>240.7734830736777</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -7976,10 +7976,10 @@
         <v>471.5549969890509</v>
       </c>
       <c r="N2" t="n">
-        <v>644.138833103312</v>
+        <v>777.3653500296342</v>
       </c>
       <c r="O2" t="n">
-        <v>374.4816735941929</v>
+        <v>0.4816735941929551</v>
       </c>
       <c r="P2" t="n">
         <v>314.7432258698271</v>
@@ -8201,10 +8201,10 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>373.8993027275024</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>321.3286984924623</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -8213,16 +8213,16 @@
         <v>845.554996989051</v>
       </c>
       <c r="N5" t="n">
-        <v>777.3653500296342</v>
+        <v>637.6540577531742</v>
       </c>
       <c r="O5" t="n">
-        <v>181.9983825376978</v>
+        <v>0.4816735941929551</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>502.1077446289929</v>
+        <v>128.1077446289929</v>
       </c>
       <c r="R5" t="n">
         <v>294.54111633436</v>
@@ -8444,19 +8444,19 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>308.6565929648241</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
         <v>845.554996989051</v>
       </c>
       <c r="N8" t="n">
-        <v>650.2254660083149</v>
+        <v>403.3653500296342</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4816735941929551</v>
+        <v>241.2551566678707</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>314.7432258698271</v>
       </c>
       <c r="Q8" t="n">
         <v>502.1077446289929</v>
@@ -8684,7 +8684,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>670.5492476884981</v>
+        <v>524.5661951690028</v>
       </c>
       <c r="N11" t="n">
         <v>228.3401037984784</v>
@@ -8693,10 +8693,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>447.6879293874171</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>22.18109136266131</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R11" t="n">
         <v>294.54111633436</v>
@@ -8915,16 +8915,16 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>423.779132753418</v>
+        <v>470.5539648241206</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>427.8625025125627</v>
       </c>
       <c r="M14" t="n">
-        <v>947.316745732772</v>
+        <v>472.6794111495058</v>
       </c>
       <c r="N14" t="n">
-        <v>876.3401037984806</v>
+        <v>876.3401037984816</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -9149,19 +9149,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J17" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>470.5539648241206</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>423.7791327534144</v>
       </c>
       <c r="M17" t="n">
-        <v>470.2371770759121</v>
+        <v>947.3167457327738</v>
       </c>
       <c r="N17" t="n">
-        <v>876.3401037984811</v>
+        <v>876.3401037984825</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -9386,19 +9386,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J20" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>470.5539648241206</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>423.7791327534144</v>
       </c>
       <c r="M20" t="n">
-        <v>524.5661951690028</v>
+        <v>947.3167457327738</v>
       </c>
       <c r="N20" t="n">
-        <v>228.3401037984784</v>
+        <v>876.3401037984825</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -9407,7 +9407,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>615.8520732695737</v>
+        <v>22.18109136266131</v>
       </c>
       <c r="R20" t="n">
         <v>294.54111633436</v>
@@ -9623,19 +9623,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K23" t="n">
-        <v>470.5539648241206</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>427.8625025125627</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>299.3167457327696</v>
+        <v>947.3167457327738</v>
       </c>
       <c r="N23" t="n">
-        <v>876.3401037984811</v>
+        <v>276.1435180588283</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -9644,7 +9644,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>195.5437567793977</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R23" t="n">
         <v>294.54111633436</v>
@@ -9860,19 +9860,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K26" t="n">
-        <v>470.5539648241206</v>
+        <v>270.9005077073871</v>
       </c>
       <c r="L26" t="n">
-        <v>427.8625025125627</v>
+        <v>428.8625025125627</v>
       </c>
       <c r="M26" t="n">
-        <v>472.679411149509</v>
+        <v>299.3167457327696</v>
       </c>
       <c r="N26" t="n">
-        <v>876.3401037984784</v>
+        <v>228.3401037984784</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -9881,7 +9881,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>22.18109136266131</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R26" t="n">
         <v>294.54111633436</v>
@@ -10097,19 +10097,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K29" t="n">
-        <v>470.5539648241206</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>427.8625025125627</v>
+        <v>428.8625025125627</v>
       </c>
       <c r="M29" t="n">
-        <v>947.3167457327697</v>
+        <v>570.2172534401566</v>
       </c>
       <c r="N29" t="n">
-        <v>401.7027692152176</v>
+        <v>228.3401037984784</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -10118,7 +10118,7 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>22.18109136266131</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R29" t="n">
         <v>294.54111633436</v>
@@ -10337,16 +10337,16 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>470.5539648241206</v>
+        <v>425.7387287130186</v>
       </c>
       <c r="L32" t="n">
-        <v>427.8625025125627</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>472.679411149509</v>
+        <v>948.3167457327697</v>
       </c>
       <c r="N32" t="n">
-        <v>876.3401037984784</v>
+        <v>877.3401037984784</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -10571,19 +10571,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J35" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>383.5539648241318</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>253.2942842685743</v>
       </c>
       <c r="M35" t="n">
-        <v>860.3167457327716</v>
+        <v>860.3167457327697</v>
       </c>
       <c r="N35" t="n">
-        <v>228.7756866567987</v>
+        <v>789.3401037984784</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -10656,13 +10656,13 @@
         <v>295.8802408630135</v>
       </c>
       <c r="L36" t="n">
-        <v>385.8777148754549</v>
+        <v>388.0893364597981</v>
       </c>
       <c r="M36" t="n">
         <v>471.6948204301074</v>
       </c>
       <c r="N36" t="n">
-        <v>485.4085271713503</v>
+        <v>483.1969055870521</v>
       </c>
       <c r="O36" t="n">
         <v>382.6817988009037</v>
@@ -10817,19 +10817,19 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>299.3167457327696</v>
+        <v>683.3062934151874</v>
       </c>
       <c r="N38" t="n">
-        <v>251.6417220935244</v>
+        <v>228.3401037984784</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>360.6879293874152</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>583.1810913626614</v>
+        <v>583.1810913626613</v>
       </c>
       <c r="R38" t="n">
         <v>294.54111633436</v>
@@ -10893,13 +10893,13 @@
         <v>295.8802408630135</v>
       </c>
       <c r="L39" t="n">
-        <v>388.0893364597981</v>
+        <v>385.8777148754926</v>
       </c>
       <c r="M39" t="n">
         <v>471.6948204301074</v>
       </c>
       <c r="N39" t="n">
-        <v>483.1969055870145</v>
+        <v>485.4085271713503</v>
       </c>
       <c r="O39" t="n">
         <v>382.6817988009037</v>
@@ -11045,19 +11045,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J41" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>253.2942842685743</v>
       </c>
       <c r="M41" t="n">
-        <v>683.306293415229</v>
+        <v>860.3167457327697</v>
       </c>
       <c r="N41" t="n">
-        <v>228.3401037984784</v>
+        <v>789.3401037984784</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -11066,7 +11066,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>583.1810913626632</v>
+        <v>22.18109136266131</v>
       </c>
       <c r="R41" t="n">
         <v>294.54111633436</v>
@@ -11136,7 +11136,7 @@
         <v>471.6948204301074</v>
       </c>
       <c r="N42" t="n">
-        <v>483.1969055870218</v>
+        <v>483.1969055870447</v>
       </c>
       <c r="O42" t="n">
         <v>382.6817988009037</v>
@@ -11282,19 +11282,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K44" t="n">
-        <v>383.5539648241316</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>340.8625025125739</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>299.3167457327696</v>
+        <v>860.3167457327697</v>
       </c>
       <c r="N44" t="n">
-        <v>318.2179207303872</v>
+        <v>228.3401037984784</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -11303,7 +11303,7 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>583.181091362665</v>
+        <v>406.1706390450789</v>
       </c>
       <c r="R44" t="n">
         <v>294.54111633436</v>
@@ -11367,13 +11367,13 @@
         <v>295.8802408630135</v>
       </c>
       <c r="L45" t="n">
-        <v>388.0893364597981</v>
+        <v>385.8777148754926</v>
       </c>
       <c r="M45" t="n">
         <v>471.6948204301074</v>
       </c>
       <c r="N45" t="n">
-        <v>483.1969055870292</v>
+        <v>485.4085271713503</v>
       </c>
       <c r="O45" t="n">
         <v>382.6817988009037</v>
@@ -22527,7 +22527,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>1.596816457606004e-12</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -23274,7 +23274,7 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.956056855791758</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
@@ -23286,7 +23286,7 @@
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>2.956056855791473</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -23460,7 +23460,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.95605685579136</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
@@ -23478,7 +23478,7 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>2.95605685575967</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -23715,7 +23715,7 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>2.956056855776779</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -23766,7 +23766,7 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>2.956056855791672</v>
       </c>
     </row>
     <row r="18">
@@ -23952,7 +23952,7 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>2.956056855776779</v>
+        <v>2.95605685579163</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -24423,7 +24423,7 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>2.956056855791442</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -24645,7 +24645,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2.956056855791587</v>
+        <v>0</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
@@ -24900,7 +24900,7 @@
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>2.95605685579163</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -25119,7 +25119,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0</v>
+        <v>4.585656855791683</v>
       </c>
       <c r="C35" t="n">
         <v>0</v>
@@ -25182,7 +25182,7 @@
         <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>4.585656855756213</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
         <v>0</v>
@@ -25356,7 +25356,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4.585656855748908</v>
+        <v>0</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
@@ -25374,7 +25374,7 @@
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>4.585656855719357</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -25593,7 +25593,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4.585656855748908</v>
+        <v>4.585656855791683</v>
       </c>
       <c r="C41" t="n">
         <v>0</v>
@@ -25845,7 +25845,7 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>4.585656855749047</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -25899,7 +25899,7 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>4.585656855791882</v>
       </c>
     </row>
     <row r="45">
@@ -26118,7 +26118,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>3717547.02147809</v>
+        <v>3717547.021478091</v>
       </c>
     </row>
     <row r="7">
@@ -26126,7 +26126,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4441553.520947043</v>
+        <v>4441553.520947044</v>
       </c>
     </row>
     <row r="8">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6613573.019353894</v>
+        <v>6613802.873227698</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7337579.518822843</v>
+        <v>7337944.671418937</v>
       </c>
     </row>
     <row r="12">
@@ -26166,7 +26166,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>8061586.018291797</v>
+        <v>8062086.469610181</v>
       </c>
     </row>
     <row r="13">
@@ -26174,7 +26174,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>8777263.500960385</v>
+        <v>8777669.397127254</v>
       </c>
     </row>
     <row r="14">
@@ -26182,7 +26182,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>9501195.413637344</v>
+        <v>9501601.309804214</v>
       </c>
     </row>
     <row r="15">
@@ -26190,7 +26190,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>10225127.3263143</v>
+        <v>10225533.22248117</v>
       </c>
     </row>
     <row r="16">
@@ -26198,7 +26198,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>10949059.23899126</v>
+        <v>10949465.13515813</v>
       </c>
     </row>
   </sheetData>
@@ -26269,49 +26269,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1479768.022390798</v>
+        <v>1479768.022390799</v>
       </c>
       <c r="C2" t="n">
-        <v>1479768.0223908</v>
+        <v>1479768.022390799</v>
       </c>
       <c r="D2" t="n">
-        <v>1479768.0223908</v>
+        <v>1479768.022390799</v>
       </c>
       <c r="E2" t="n">
         <v>1479491.542393077</v>
       </c>
       <c r="F2" t="n">
-        <v>1479491.542393078</v>
+        <v>1479491.542393079</v>
       </c>
       <c r="G2" t="n">
         <v>1479491.542393077</v>
       </c>
       <c r="H2" t="n">
-        <v>1479491.542393078</v>
+        <v>1479491.542393076</v>
       </c>
       <c r="I2" t="n">
-        <v>1479491.542393077</v>
+        <v>1479491.542393076</v>
       </c>
       <c r="J2" t="n">
-        <v>1479491.542393077</v>
+        <v>1479768.0223908</v>
       </c>
       <c r="K2" t="n">
-        <v>1479491.542393077</v>
+        <v>1479768.0223908</v>
       </c>
       <c r="L2" t="n">
-        <v>1479491.542393077</v>
+        <v>1479768.022390799</v>
       </c>
       <c r="M2" t="n">
-        <v>1479339.12590508</v>
+        <v>1479339.125905077</v>
       </c>
       <c r="N2" t="n">
-        <v>1479339.125905081</v>
+        <v>1479339.125905083</v>
       </c>
       <c r="O2" t="n">
-        <v>1479339.125905081</v>
+        <v>1479339.125905076</v>
       </c>
       <c r="P2" t="n">
-        <v>1479339.125905081</v>
+        <v>1479339.125905077</v>
       </c>
     </row>
     <row r="3">
@@ -26345,7 +26345,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>388448</v>
+        <v>388800</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -26354,7 +26354,7 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>85024.00000000389</v>
+        <v>84672</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>602166.8573620638</v>
+        <v>601967.7658514546</v>
       </c>
       <c r="C4" t="n">
-        <v>600158.4933044576</v>
+        <v>599959.4017938484</v>
       </c>
       <c r="D4" t="n">
-        <v>598147.4047756541</v>
+        <v>597948.3132650448</v>
       </c>
       <c r="E4" t="n">
-        <v>513949.0290844531</v>
+        <v>513751.7523916513</v>
       </c>
       <c r="F4" t="n">
-        <v>512264.4313324891</v>
+        <v>512067.1546396887</v>
       </c>
       <c r="G4" t="n">
-        <v>510577.5088988319</v>
+        <v>510380.2322060294</v>
       </c>
       <c r="H4" t="n">
-        <v>508888.2451130988</v>
+        <v>508690.9684202963</v>
       </c>
       <c r="I4" t="n">
-        <v>507196.6230877017</v>
+        <v>506999.3463948999</v>
       </c>
       <c r="J4" t="n">
-        <v>505502.6257137285</v>
+        <v>505362.3521738978</v>
       </c>
       <c r="K4" t="n">
-        <v>503806.2356567227</v>
+        <v>503666.1331422089</v>
       </c>
       <c r="L4" t="n">
-        <v>502107.4353523577</v>
+        <v>501967.5041061556</v>
       </c>
       <c r="M4" t="n">
-        <v>506489.4162279245</v>
+        <v>506308.9084534669</v>
       </c>
       <c r="N4" t="n">
-        <v>504723.3213042072</v>
+        <v>504542.8135297527</v>
       </c>
       <c r="O4" t="n">
-        <v>502954.6717247903</v>
+        <v>502774.1639503327</v>
       </c>
       <c r="P4" t="n">
-        <v>501183.4482814753</v>
+        <v>501002.9405070178</v>
       </c>
     </row>
     <row r="5">
@@ -26449,25 +26449,25 @@
         <v>73949.149</v>
       </c>
       <c r="J5" t="n">
-        <v>73949.149</v>
+        <v>74009.94899999999</v>
       </c>
       <c r="K5" t="n">
-        <v>73949.149</v>
+        <v>74009.94899999999</v>
       </c>
       <c r="L5" t="n">
-        <v>73949.149</v>
+        <v>74009.94899999999</v>
       </c>
       <c r="M5" t="n">
-        <v>70677.20500000067</v>
+        <v>70677.20499999999</v>
       </c>
       <c r="N5" t="n">
-        <v>70677.20500000067</v>
+        <v>70677.20499999999</v>
       </c>
       <c r="O5" t="n">
-        <v>70677.20500000067</v>
+        <v>70677.20499999999</v>
       </c>
       <c r="P5" t="n">
-        <v>70677.20500000067</v>
+        <v>70677.20499999999</v>
       </c>
     </row>
     <row r="6">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>586915.9650287346</v>
+        <v>587115.0565393446</v>
       </c>
       <c r="C6" t="n">
-        <v>820997.329086342</v>
+        <v>821196.420596951</v>
       </c>
       <c r="D6" t="n">
-        <v>823008.4176151456</v>
+        <v>823207.5091257544</v>
       </c>
       <c r="E6" t="n">
-        <v>300445.3643086236</v>
+        <v>300642.641001426</v>
       </c>
       <c r="F6" t="n">
-        <v>893277.9620605889</v>
+        <v>893475.2387533906</v>
       </c>
       <c r="G6" t="n">
-        <v>894964.8844942455</v>
+        <v>895162.1611870476</v>
       </c>
       <c r="H6" t="n">
-        <v>896654.1482799796</v>
+        <v>896851.42497278</v>
       </c>
       <c r="I6" t="n">
-        <v>898345.7703053752</v>
+        <v>898543.0469981765</v>
       </c>
       <c r="J6" t="n">
-        <v>511591.7676793488</v>
+        <v>511595.7212169018</v>
       </c>
       <c r="K6" t="n">
-        <v>901736.1577363543</v>
+        <v>902091.9402485909</v>
       </c>
       <c r="L6" t="n">
-        <v>903434.9580407195</v>
+        <v>903790.5692846437</v>
       </c>
       <c r="M6" t="n">
-        <v>817148.5046771506</v>
+        <v>817681.0124516102</v>
       </c>
       <c r="N6" t="n">
-        <v>903938.5996008733</v>
+        <v>904119.1073753309</v>
       </c>
       <c r="O6" t="n">
-        <v>648907.2491802898</v>
+        <v>649087.7569547436</v>
       </c>
       <c r="P6" t="n">
-        <v>907478.4726236049</v>
+        <v>907658.9803980588</v>
       </c>
     </row>
   </sheetData>
@@ -26883,25 +26883,25 @@
         <v>648</v>
       </c>
       <c r="J4" t="n">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="K4" t="n">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="L4" t="n">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="M4" t="n">
-        <v>561.000000000011</v>
+        <v>561</v>
       </c>
       <c r="N4" t="n">
-        <v>561.000000000011</v>
+        <v>561</v>
       </c>
       <c r="O4" t="n">
-        <v>561.000000000011</v>
+        <v>561</v>
       </c>
       <c r="P4" t="n">
-        <v>561.000000000011</v>
+        <v>561</v>
       </c>
     </row>
   </sheetData>
@@ -26972,7 +26972,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C2" t="n">
         <v>-0</v>
@@ -26987,7 +26987,7 @@
         <v>-0</v>
       </c>
       <c r="G2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>-0</v>
@@ -26999,7 +26999,7 @@
         <v>321</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L2" t="n">
         <v>-0</v>
@@ -27008,7 +27008,7 @@
         <v>24</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O2" t="n">
         <v>321</v>
@@ -27100,7 +27100,7 @@
         <v>-0</v>
       </c>
       <c r="J4" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="K4" t="n">
         <v>-0</v>
@@ -27109,7 +27109,7 @@
         <v>-0</v>
       </c>
       <c r="M4" t="n">
-        <v>187.0000000000039</v>
+        <v>186</v>
       </c>
       <c r="N4" t="n">
         <v>-0</v>
@@ -27448,7 +27448,7 @@
         <v>400</v>
       </c>
       <c r="G2" t="n">
-        <v>398.046593539207</v>
+        <v>400</v>
       </c>
       <c r="H2" t="n">
         <v>400</v>
@@ -27481,7 +27481,7 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>224.8682520946261</v>
+        <v>222.9148456338345</v>
       </c>
       <c r="S2" t="n">
         <v>400</v>
@@ -27512,16 +27512,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>384.5565566463266</v>
+        <v>10.55655664632661</v>
       </c>
       <c r="C3" t="n">
         <v>361.0999124455193</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F3" t="n">
         <v>339.6362423378769</v>
@@ -27533,7 +27533,7 @@
         <v>330.0284079411381</v>
       </c>
       <c r="I3" t="n">
-        <v>41.7794497563419</v>
+        <v>209.4985557026693</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -27557,7 +27557,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>144.7989632036872</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>400</v>
@@ -27578,7 +27578,7 @@
         <v>400</v>
       </c>
       <c r="X3" t="n">
-        <v>400</v>
+        <v>60.47007313774441</v>
       </c>
       <c r="Y3" t="n">
         <v>399.3913927661343</v>
@@ -27591,10 +27591,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>400</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C4" t="n">
-        <v>400</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D4" t="n">
         <v>285.5362180555555</v>
@@ -27603,22 +27603,22 @@
         <v>400</v>
       </c>
       <c r="F4" t="n">
-        <v>293.2347948311275</v>
+        <v>400</v>
       </c>
       <c r="G4" t="n">
-        <v>244.858135136612</v>
+        <v>400</v>
       </c>
       <c r="H4" t="n">
-        <v>227.1197490524383</v>
+        <v>400</v>
       </c>
       <c r="I4" t="n">
         <v>400</v>
       </c>
       <c r="J4" t="n">
-        <v>396.1372930982029</v>
+        <v>22.13729309820286</v>
       </c>
       <c r="K4" t="n">
-        <v>266.941429538848</v>
+        <v>400</v>
       </c>
       <c r="L4" t="n">
         <v>400</v>
@@ -27648,7 +27648,7 @@
         <v>400</v>
       </c>
       <c r="U4" t="n">
-        <v>150.9482601269169</v>
+        <v>349.819676270712</v>
       </c>
       <c r="V4" t="n">
         <v>199.1703102162162</v>
@@ -27657,7 +27657,7 @@
         <v>226.3728098387097</v>
       </c>
       <c r="X4" t="n">
-        <v>400</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y4" t="n">
         <v>287.4653528494624</v>
@@ -27691,7 +27691,7 @@
         <v>400</v>
       </c>
       <c r="I5" t="n">
-        <v>132.1643059857122</v>
+        <v>132.1643059857123</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -27752,16 +27752,16 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
         <v>325.517988705216</v>
@@ -27809,10 +27809,10 @@
         <v>400</v>
       </c>
       <c r="V6" t="n">
-        <v>400</v>
+        <v>240.0883178788022</v>
       </c>
       <c r="W6" t="n">
-        <v>267.8628177939761</v>
+        <v>58.37314290982852</v>
       </c>
       <c r="X6" t="n">
         <v>400</v>
@@ -27849,16 +27849,16 @@
         <v>400</v>
       </c>
       <c r="I7" t="n">
-        <v>400</v>
+        <v>171.047816275856</v>
       </c>
       <c r="J7" t="n">
-        <v>122.6068625706611</v>
+        <v>22.13729309820286</v>
       </c>
       <c r="K7" t="n">
         <v>266.941429538848</v>
       </c>
       <c r="L7" t="n">
-        <v>395.9334970102382</v>
+        <v>399.1717054756575</v>
       </c>
       <c r="M7" t="n">
         <v>400</v>
@@ -27891,10 +27891,10 @@
         <v>199.1703102162162</v>
       </c>
       <c r="W7" t="n">
-        <v>226.3728098387097</v>
+        <v>400</v>
       </c>
       <c r="X7" t="n">
-        <v>247.4436454301076</v>
+        <v>400</v>
       </c>
       <c r="Y7" t="n">
         <v>400</v>
@@ -27925,7 +27925,7 @@
         <v>400</v>
       </c>
       <c r="H8" t="n">
-        <v>398.0465935392086</v>
+        <v>400</v>
       </c>
       <c r="I8" t="n">
         <v>134.1177124465037</v>
@@ -27955,7 +27955,7 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>224.8682520946261</v>
+        <v>222.9148456338345</v>
       </c>
       <c r="S8" t="n">
         <v>400</v>
@@ -27986,28 +27986,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>384.5565566463266</v>
+        <v>10.55655664632661</v>
       </c>
       <c r="C9" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E9" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G9" t="n">
         <v>325.517988705216</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>330.0284079411381</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>209.4985557026693</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -28031,10 +28031,10 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>38.72409409996035</v>
       </c>
       <c r="R9" t="n">
-        <v>240.1152904142128</v>
+        <v>400</v>
       </c>
       <c r="S9" t="n">
         <v>400</v>
@@ -28071,7 +28071,7 @@
         <v>400</v>
       </c>
       <c r="D10" t="n">
-        <v>290.3161688374341</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E10" t="n">
         <v>280.9809048369565</v>
@@ -28092,7 +28092,7 @@
         <v>22.13729309820286</v>
       </c>
       <c r="K10" t="n">
-        <v>266.941429538848</v>
+        <v>271.7213803207266</v>
       </c>
       <c r="L10" t="n">
         <v>400</v>
@@ -28226,16 +28226,16 @@
         <v>321</v>
       </c>
       <c r="C12" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="F12" t="n">
-        <v>137.8407332208561</v>
+        <v>321</v>
       </c>
       <c r="G12" t="n">
         <v>321</v>
@@ -28283,16 +28283,16 @@
         <v>321</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="W12" t="n">
         <v>321</v>
       </c>
       <c r="X12" t="n">
-        <v>321</v>
+        <v>137.8407332208562</v>
       </c>
       <c r="Y12" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -28326,7 +28326,7 @@
         <v>321</v>
       </c>
       <c r="J13" t="n">
-        <v>315.8198010595347</v>
+        <v>321</v>
       </c>
       <c r="K13" t="n">
         <v>321</v>
@@ -28371,7 +28371,7 @@
         <v>321</v>
       </c>
       <c r="Y13" t="n">
-        <v>321</v>
+        <v>315.8198010595348</v>
       </c>
     </row>
     <row r="14">
@@ -28429,7 +28429,7 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>163.2515083760331</v>
+        <v>163.2515083760651</v>
       </c>
       <c r="S14" t="n">
         <v>321</v>
@@ -28460,7 +28460,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="C15" t="n">
         <v>321</v>
@@ -28517,10 +28517,10 @@
         <v>321</v>
       </c>
       <c r="U15" t="n">
-        <v>321</v>
+        <v>137.8407332208563</v>
       </c>
       <c r="V15" t="n">
-        <v>137.8407332208564</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
@@ -28593,22 +28593,22 @@
         <v>321</v>
       </c>
       <c r="T16" t="n">
+        <v>321</v>
+      </c>
+      <c r="U16" t="n">
+        <v>321</v>
+      </c>
+      <c r="V16" t="n">
+        <v>321</v>
+      </c>
+      <c r="W16" t="n">
+        <v>321</v>
+      </c>
+      <c r="X16" t="n">
+        <v>321</v>
+      </c>
+      <c r="Y16" t="n">
         <v>315.8198010595348</v>
-      </c>
-      <c r="U16" t="n">
-        <v>321</v>
-      </c>
-      <c r="V16" t="n">
-        <v>321</v>
-      </c>
-      <c r="W16" t="n">
-        <v>321</v>
-      </c>
-      <c r="X16" t="n">
-        <v>321</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>321</v>
       </c>
     </row>
     <row r="17">
@@ -28666,7 +28666,7 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>163.2515083760483</v>
+        <v>163.2515083760331</v>
       </c>
       <c r="S17" t="n">
         <v>321</v>
@@ -28697,19 +28697,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="D18" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
         <v>321</v>
@@ -28760,13 +28760,13 @@
         <v>321</v>
       </c>
       <c r="W18" t="n">
-        <v>137.8407332208565</v>
+        <v>321</v>
       </c>
       <c r="X18" t="n">
-        <v>321</v>
+        <v>137.8407332208562</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
     </row>
     <row r="19">
@@ -28903,7 +28903,7 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>163.2515083760483</v>
+        <v>163.2515083760331</v>
       </c>
       <c r="S20" t="n">
         <v>321</v>
@@ -28934,16 +28934,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>137.8407332208562</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="F21" t="n">
         <v>321</v>
@@ -29000,10 +29000,10 @@
         <v>321</v>
       </c>
       <c r="X21" t="n">
-        <v>321</v>
+        <v>137.8407332208565</v>
       </c>
       <c r="Y21" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -29022,7 +29022,7 @@
         <v>321</v>
       </c>
       <c r="E22" t="n">
-        <v>321</v>
+        <v>315.8198010595347</v>
       </c>
       <c r="F22" t="n">
         <v>321</v>
@@ -29037,7 +29037,7 @@
         <v>321</v>
       </c>
       <c r="J22" t="n">
-        <v>315.8198010595347</v>
+        <v>321</v>
       </c>
       <c r="K22" t="n">
         <v>321</v>
@@ -29171,13 +29171,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="C24" t="n">
         <v>321</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="E24" t="n">
         <v>321</v>
@@ -29228,19 +29228,19 @@
         <v>321</v>
       </c>
       <c r="U24" t="n">
-        <v>321</v>
+        <v>137.8407332208563</v>
       </c>
       <c r="V24" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>137.8407332208565</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
     </row>
     <row r="25">
@@ -29347,7 +29347,7 @@
         <v>321</v>
       </c>
       <c r="H26" t="n">
-        <v>321</v>
+        <v>320.0752568557915</v>
       </c>
       <c r="I26" t="n">
         <v>96.3013908384635</v>
@@ -29453,10 +29453,10 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>77.80484999613995</v>
       </c>
       <c r="R27" t="n">
-        <v>215.6455832169961</v>
+        <v>321</v>
       </c>
       <c r="S27" t="n">
         <v>321</v>
@@ -29468,13 +29468,13 @@
         <v>321</v>
       </c>
       <c r="V27" t="n">
-        <v>321</v>
+        <v>137.8407332208564</v>
       </c>
       <c r="W27" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="Y27" t="n">
         <v>0</v>
@@ -29502,7 +29502,7 @@
         <v>321</v>
       </c>
       <c r="G28" t="n">
-        <v>321</v>
+        <v>315.8198010595347</v>
       </c>
       <c r="H28" t="n">
         <v>321</v>
@@ -29511,7 +29511,7 @@
         <v>321</v>
       </c>
       <c r="J28" t="n">
-        <v>315.8198010595347</v>
+        <v>321</v>
       </c>
       <c r="K28" t="n">
         <v>321</v>
@@ -29578,7 +29578,7 @@
         <v>321</v>
       </c>
       <c r="F29" t="n">
-        <v>321</v>
+        <v>320.0752568557916</v>
       </c>
       <c r="G29" t="n">
         <v>321</v>
@@ -29645,19 +29645,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="C30" t="n">
         <v>321</v>
       </c>
       <c r="D30" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
         <v>321</v>
@@ -29666,7 +29666,7 @@
         <v>321</v>
       </c>
       <c r="I30" t="n">
-        <v>191.4287443819146</v>
+        <v>86.07432759891078</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -29693,7 +29693,7 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>215.6455832169961</v>
+        <v>321</v>
       </c>
       <c r="S30" t="n">
         <v>321</v>
@@ -29711,10 +29711,10 @@
         <v>321</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
     </row>
     <row r="31">
@@ -29781,7 +29781,7 @@
         <v>321</v>
       </c>
       <c r="U31" t="n">
-        <v>315.8198010595348</v>
+        <v>315.8198010595347</v>
       </c>
       <c r="V31" t="n">
         <v>321</v>
@@ -29851,7 +29851,7 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>163.2515083760331</v>
+        <v>162.3267652318248</v>
       </c>
       <c r="S32" t="n">
         <v>321</v>
@@ -29888,7 +29888,7 @@
         <v>321</v>
       </c>
       <c r="D33" t="n">
-        <v>137.8407332208561</v>
+        <v>321</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -29897,7 +29897,7 @@
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>321</v>
+        <v>215.6455832169961</v>
       </c>
       <c r="H33" t="n">
         <v>321</v>
@@ -29927,7 +29927,7 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>77.80484999613995</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
         <v>321</v>
@@ -29945,10 +29945,10 @@
         <v>321</v>
       </c>
       <c r="W33" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="Y33" t="n">
         <v>321</v>
@@ -29988,7 +29988,7 @@
         <v>321</v>
       </c>
       <c r="K34" t="n">
-        <v>321</v>
+        <v>315.8198010595346</v>
       </c>
       <c r="L34" t="n">
         <v>321</v>
@@ -30027,7 +30027,7 @@
         <v>321</v>
       </c>
       <c r="X34" t="n">
-        <v>315.8198010595348</v>
+        <v>321</v>
       </c>
       <c r="Y34" t="n">
         <v>321</v>
@@ -30119,16 +30119,16 @@
         </is>
       </c>
       <c r="B36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" t="n">
         <v>345</v>
       </c>
-      <c r="C36" t="n">
-        <v>345</v>
-      </c>
-      <c r="D36" t="n">
-        <v>0</v>
-      </c>
       <c r="E36" t="n">
-        <v>190.6528838351547</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F36" t="n">
         <v>339.6362423378769</v>
@@ -30140,7 +30140,7 @@
         <v>324.959653224157</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>191.4287443819146</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -30164,10 +30164,10 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>1.552042231283821</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="S36" t="n">
         <v>345</v>
@@ -30182,13 +30182,13 @@
         <v>345</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="X36" t="n">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>345</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -30325,7 +30325,7 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>163.2515083760331</v>
+        <v>163.2515083761057</v>
       </c>
       <c r="S38" t="n">
         <v>345</v>
@@ -30356,13 +30356,13 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>345</v>
+        <v>261.0555317949406</v>
       </c>
       <c r="C39" t="n">
         <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
@@ -30374,10 +30374,10 @@
         <v>324.9931585165368</v>
       </c>
       <c r="H39" t="n">
-        <v>165.2487793971815</v>
+        <v>324.959653224157</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>191.4287443819146</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -30401,7 +30401,7 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>77.80484999613995</v>
       </c>
       <c r="R39" t="n">
         <v>345</v>
@@ -30438,13 +30438,13 @@
         <v>345</v>
       </c>
       <c r="C40" t="n">
+        <v>272.7252466480447</v>
+      </c>
+      <c r="D40" t="n">
         <v>345</v>
       </c>
-      <c r="D40" t="n">
-        <v>285.5362180555555</v>
-      </c>
       <c r="E40" t="n">
-        <v>345</v>
+        <v>280.9809048369565</v>
       </c>
       <c r="F40" t="n">
         <v>345</v>
@@ -30456,13 +30456,13 @@
         <v>345</v>
       </c>
       <c r="I40" t="n">
-        <v>157.815816275856</v>
+        <v>345</v>
       </c>
       <c r="J40" t="n">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>224.7102824092685</v>
+        <v>313.5264754718946</v>
       </c>
       <c r="L40" t="n">
         <v>330.5174970102382</v>
@@ -30495,7 +30495,7 @@
         <v>345</v>
       </c>
       <c r="V40" t="n">
-        <v>199.1703102162162</v>
+        <v>345</v>
       </c>
       <c r="W40" t="n">
         <v>345</v>
@@ -30602,19 +30602,19 @@
         <v>345</v>
       </c>
       <c r="E42" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
         <v>339.6362423378769</v>
       </c>
       <c r="G42" t="n">
-        <v>324.9931585165368</v>
+        <v>150.6056955758118</v>
       </c>
       <c r="H42" t="n">
-        <v>324.959653224157</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>191.4287443819146</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -30638,16 +30638,16 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.552042231313536</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="U42" t="n">
         <v>345</v>
@@ -30656,10 +30656,10 @@
         <v>345</v>
       </c>
       <c r="W42" t="n">
+        <v>0</v>
+      </c>
+      <c r="X42" t="n">
         <v>345</v>
-      </c>
-      <c r="X42" t="n">
-        <v>0</v>
       </c>
       <c r="Y42" t="n">
         <v>345</v>
@@ -30675,13 +30675,13 @@
         <v>345</v>
       </c>
       <c r="C43" t="n">
-        <v>345</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D43" t="n">
-        <v>345</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E43" t="n">
-        <v>345</v>
+        <v>325.9843967682623</v>
       </c>
       <c r="F43" t="n">
         <v>345</v>
@@ -30696,10 +30696,10 @@
         <v>345</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="K43" t="n">
-        <v>313.7737196794415</v>
+        <v>345</v>
       </c>
       <c r="L43" t="n">
         <v>330.5174970102382</v>
@@ -30729,19 +30729,19 @@
         <v>345</v>
       </c>
       <c r="U43" t="n">
-        <v>150.9242601269169</v>
+        <v>345</v>
       </c>
       <c r="V43" t="n">
-        <v>345</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W43" t="n">
-        <v>345</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X43" t="n">
-        <v>345</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y43" t="n">
-        <v>345</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="44">
@@ -30833,25 +30833,25 @@
         <v>345</v>
       </c>
       <c r="C45" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" t="n">
         <v>345</v>
       </c>
-      <c r="D45" t="n">
-        <v>190.652883835133</v>
-      </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F45" t="n">
         <v>339.6362423378769</v>
       </c>
       <c r="G45" t="n">
-        <v>324.9931585165368</v>
+        <v>306.5048539719845</v>
       </c>
       <c r="H45" t="n">
-        <v>324.959653224157</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>191.4287443819146</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -30878,10 +30878,10 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="T45" t="n">
         <v>345</v>
@@ -30893,10 +30893,10 @@
         <v>345</v>
       </c>
       <c r="W45" t="n">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
         <v>345</v>
@@ -30918,22 +30918,22 @@
         <v>345</v>
       </c>
       <c r="E46" t="n">
-        <v>345</v>
+        <v>280.9809048369565</v>
       </c>
       <c r="F46" t="n">
-        <v>345</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G46" t="n">
-        <v>345</v>
+        <v>244.418135136612</v>
       </c>
       <c r="H46" t="n">
-        <v>345</v>
+        <v>223.2077490524383</v>
       </c>
       <c r="I46" t="n">
         <v>345</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>272.3168335432779</v>
       </c>
       <c r="K46" t="n">
         <v>345</v>
@@ -30966,19 +30966,19 @@
         <v>345</v>
       </c>
       <c r="U46" t="n">
-        <v>251.0451666003805</v>
+        <v>345</v>
       </c>
       <c r="V46" t="n">
-        <v>199.1703102162162</v>
+        <v>345</v>
       </c>
       <c r="W46" t="n">
         <v>345</v>
       </c>
       <c r="X46" t="n">
-        <v>345</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y46" t="n">
-        <v>345</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
   </sheetData>
@@ -34743,22 +34743,22 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1006972724976123</v>
+        <v>240.8741803461753</v>
       </c>
       <c r="K2" t="n">
         <v>52.67130150753769</v>
       </c>
       <c r="L2" t="n">
-        <v>65.3434070351759</v>
+        <v>65.34340703517586</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>240.7734830736777</v>
+        <v>374</v>
       </c>
       <c r="O2" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
         <v>374</v>
@@ -34877,10 +34877,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>112.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>127.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -34889,22 +34889,22 @@
         <v>119.0190951630435</v>
       </c>
       <c r="F4" t="n">
-        <v>18.85193886338563</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>155.141864863388</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>172.8802509475617</v>
       </c>
       <c r="I4" t="n">
         <v>228.952183724144</v>
       </c>
       <c r="J4" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>133.058570461152</v>
       </c>
       <c r="L4" t="n">
         <v>4.06650298976183</v>
@@ -34934,7 +34934,7 @@
         <v>190.7690400511193</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>198.871416143795</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -34943,7 +34943,7 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>152.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
@@ -34980,28 +34980,28 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1006972724976123</v>
+        <v>374</v>
       </c>
       <c r="K5" t="n">
-        <v>52.67130150753769</v>
+        <v>373.9999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>65.3434070351759</v>
+        <v>65.34340703517591</v>
       </c>
       <c r="M5" t="n">
         <v>374</v>
       </c>
       <c r="N5" t="n">
-        <v>374</v>
+        <v>234.28870772354</v>
       </c>
       <c r="O5" t="n">
-        <v>181.5167089435048</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
         <v>59.25677413017286</v>
       </c>
       <c r="Q5" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -35135,16 +35135,16 @@
         <v>172.8802509475617</v>
       </c>
       <c r="I7" t="n">
-        <v>228.952183724144</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>100.4695694724582</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>3.238208465419267</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -35177,10 +35177,10 @@
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>173.6271901612903</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y7" t="n">
         <v>112.5346471505376</v>
@@ -35223,19 +35223,19 @@
         <v>52.67130150753769</v>
       </c>
       <c r="L8" t="n">
-        <v>374</v>
+        <v>65.3434070351759</v>
       </c>
       <c r="M8" t="n">
         <v>374</v>
       </c>
       <c r="N8" t="n">
-        <v>246.8601159786807</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>240.7734830736778</v>
       </c>
       <c r="P8" t="n">
-        <v>59.25677413017286</v>
+        <v>374</v>
       </c>
       <c r="Q8" t="n">
         <v>374</v>
@@ -35357,28 +35357,28 @@
         <v>127.2747533519553</v>
       </c>
       <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
         <v>4.779950781878574</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>4.06650298976183</v>
@@ -35463,7 +35463,7 @@
         <v>220.1374974874373</v>
       </c>
       <c r="M11" t="n">
-        <v>371.2325019557286</v>
+        <v>225.2494494362332</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -35472,10 +35472,10 @@
         <v>164.7897032902292</v>
       </c>
       <c r="P11" t="n">
-        <v>648.0000000000019</v>
+        <v>200.3120706125849</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>593.6709819069124</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -35612,7 +35612,7 @@
         <v>163.184183724144</v>
       </c>
       <c r="J13" t="n">
-        <v>324.7905079613318</v>
+        <v>329.9707069017971</v>
       </c>
       <c r="K13" t="n">
         <v>105.178570461152</v>
@@ -35657,7 +35657,7 @@
         <v>73.55635456989245</v>
       </c>
       <c r="Y13" t="n">
-        <v>33.53464715053764</v>
+        <v>28.35444821007238</v>
       </c>
     </row>
     <row r="14">
@@ -35694,16 +35694,16 @@
         <v>83.35374249862829</v>
       </c>
       <c r="K14" t="n">
-        <v>601.2251679292974</v>
+        <v>648</v>
       </c>
       <c r="L14" t="n">
-        <v>220.1374974874373</v>
+        <v>648</v>
       </c>
       <c r="M14" t="n">
-        <v>648.0000000000024</v>
+        <v>173.3626654167362</v>
       </c>
       <c r="N14" t="n">
-        <v>648.0000000000024</v>
+        <v>648.0000000000033</v>
       </c>
       <c r="O14" t="n">
         <v>164.7897032902292</v>
@@ -35879,7 +35879,7 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>108.4688411106541</v>
+        <v>113.6490400511193</v>
       </c>
       <c r="U16" t="n">
         <v>170.0757398730831</v>
@@ -35894,7 +35894,7 @@
         <v>73.55635456989245</v>
       </c>
       <c r="Y16" t="n">
-        <v>33.53464715053764</v>
+        <v>28.35444821007238</v>
       </c>
     </row>
     <row r="17">
@@ -35928,19 +35928,19 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>513.658479084785</v>
+        <v>83.35374249862829</v>
       </c>
       <c r="K17" t="n">
-        <v>648</v>
+        <v>177.4460351758794</v>
       </c>
       <c r="L17" t="n">
-        <v>220.1374974874373</v>
+        <v>643.9166302408516</v>
       </c>
       <c r="M17" t="n">
-        <v>170.9204313431426</v>
+        <v>648.0000000000042</v>
       </c>
       <c r="N17" t="n">
-        <v>648.0000000000028</v>
+        <v>648.0000000000042</v>
       </c>
       <c r="O17" t="n">
         <v>164.7897032902292</v>
@@ -35952,7 +35952,7 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.515824502954881e-11</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -36165,19 +36165,19 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>513.658479084785</v>
+        <v>83.35374249862829</v>
       </c>
       <c r="K20" t="n">
-        <v>648</v>
+        <v>177.4460351758794</v>
       </c>
       <c r="L20" t="n">
-        <v>220.1374974874373</v>
+        <v>643.9166302408516</v>
       </c>
       <c r="M20" t="n">
-        <v>225.2494494362332</v>
+        <v>648.0000000000042</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>648.0000000000042</v>
       </c>
       <c r="O20" t="n">
         <v>164.7897032902292</v>
@@ -36186,10 +36186,10 @@
         <v>200.3120706125849</v>
       </c>
       <c r="Q20" t="n">
-        <v>593.6709819069124</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.515824502954881e-11</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -36308,7 +36308,7 @@
         <v>35.46378194444452</v>
       </c>
       <c r="E22" t="n">
-        <v>40.01909516304346</v>
+        <v>34.83889622257817</v>
       </c>
       <c r="F22" t="n">
         <v>46.61714403225807</v>
@@ -36323,7 +36323,7 @@
         <v>163.184183724144</v>
       </c>
       <c r="J22" t="n">
-        <v>324.7905079613318</v>
+        <v>329.9707069017971</v>
       </c>
       <c r="K22" t="n">
         <v>105.178570461152</v>
@@ -36402,19 +36402,19 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>83.35374249862829</v>
+        <v>513.658479084785</v>
       </c>
       <c r="K23" t="n">
-        <v>648</v>
+        <v>177.4460351758794</v>
       </c>
       <c r="L23" t="n">
-        <v>648</v>
+        <v>220.1374974874373</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>648.0000000000041</v>
       </c>
       <c r="N23" t="n">
-        <v>648.0000000000028</v>
+        <v>47.80341426034986</v>
       </c>
       <c r="O23" t="n">
         <v>164.7897032902292</v>
@@ -36423,7 +36423,7 @@
         <v>200.3120706125849</v>
       </c>
       <c r="Q23" t="n">
-        <v>173.3626654167364</v>
+        <v>593.6709819069124</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -36639,19 +36639,19 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>83.35374249862829</v>
+        <v>513.658479084785</v>
       </c>
       <c r="K26" t="n">
-        <v>648</v>
+        <v>448.3465428832665</v>
       </c>
       <c r="L26" t="n">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="M26" t="n">
-        <v>173.3626654167394</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>648</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>164.7897032902292</v>
@@ -36660,7 +36660,7 @@
         <v>200.3120706125849</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>593.6709819069124</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -36788,7 +36788,7 @@
         <v>46.61714403225807</v>
       </c>
       <c r="G28" t="n">
-        <v>76.58186486338801</v>
+        <v>71.40166592292275</v>
       </c>
       <c r="H28" t="n">
         <v>97.79225094756171</v>
@@ -36797,7 +36797,7 @@
         <v>163.184183724144</v>
       </c>
       <c r="J28" t="n">
-        <v>324.7905079613318</v>
+        <v>329.9707069017971</v>
       </c>
       <c r="K28" t="n">
         <v>105.178570461152</v>
@@ -36876,19 +36876,19 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>83.35374249862829</v>
+        <v>513.658479084785</v>
       </c>
       <c r="K29" t="n">
-        <v>648</v>
+        <v>177.4460351758794</v>
       </c>
       <c r="L29" t="n">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="M29" t="n">
-        <v>648</v>
+        <v>270.900507707387</v>
       </c>
       <c r="N29" t="n">
-        <v>173.3626654167392</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>164.7897032902292</v>
@@ -36897,7 +36897,7 @@
         <v>200.3120706125849</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>593.6709819069124</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -37067,7 +37067,7 @@
         <v>113.6490400511193</v>
       </c>
       <c r="U31" t="n">
-        <v>164.8955409326179</v>
+        <v>164.8955409326178</v>
       </c>
       <c r="V31" t="n">
         <v>121.8296897837838</v>
@@ -37116,16 +37116,16 @@
         <v>83.35374249862829</v>
       </c>
       <c r="K32" t="n">
-        <v>648</v>
+        <v>603.184763888898</v>
       </c>
       <c r="L32" t="n">
-        <v>648</v>
+        <v>220.1374974874373</v>
       </c>
       <c r="M32" t="n">
-        <v>173.3626654167394</v>
+        <v>649</v>
       </c>
       <c r="N32" t="n">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="O32" t="n">
         <v>164.7897032902292</v>
@@ -37274,7 +37274,7 @@
         <v>329.9707069017971</v>
       </c>
       <c r="K34" t="n">
-        <v>105.178570461152</v>
+        <v>99.99837152068662</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -37313,7 +37313,7 @@
         <v>94.62719016129032</v>
       </c>
       <c r="X34" t="n">
-        <v>68.37615562942723</v>
+        <v>73.55635456989245</v>
       </c>
       <c r="Y34" t="n">
         <v>33.53464715053764</v>
@@ -37350,19 +37350,19 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>513.658479084785</v>
+        <v>83.35374249862829</v>
       </c>
       <c r="K35" t="n">
-        <v>561.0000000000111</v>
+        <v>177.4460351758794</v>
       </c>
       <c r="L35" t="n">
-        <v>220.1374974874373</v>
+        <v>473.4317817560116</v>
       </c>
       <c r="M35" t="n">
-        <v>561.0000000000019</v>
+        <v>561</v>
       </c>
       <c r="N35" t="n">
-        <v>0.4355828583203045</v>
+        <v>561</v>
       </c>
       <c r="O35" t="n">
         <v>164.7897032902292</v>
@@ -37435,13 +37435,13 @@
         <v>311.6274301124894</v>
       </c>
       <c r="L36" t="n">
-        <v>433.9385745190608</v>
+        <v>436.150196103404</v>
       </c>
       <c r="M36" t="n">
         <v>276.0650421645042</v>
       </c>
       <c r="N36" t="n">
-        <v>328.7468614294096</v>
+        <v>326.5352398451114</v>
       </c>
       <c r="O36" t="n">
         <v>419.0391822801049</v>
@@ -37514,7 +37514,7 @@
         <v>129.178570461152</v>
       </c>
       <c r="L37" t="n">
-        <v>14.48250298976181</v>
+        <v>14.48250298976183</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
@@ -37541,7 +37541,7 @@
         <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>91.94025674079907</v>
+        <v>91.94025674079904</v>
       </c>
       <c r="V37" t="n">
         <v>145.8296897837838</v>
@@ -37596,19 +37596,19 @@
         <v>220.1374974874373</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>383.9895476824178</v>
       </c>
       <c r="N38" t="n">
-        <v>23.30161829504597</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>164.7897032902292</v>
       </c>
       <c r="P38" t="n">
-        <v>561.0000000000001</v>
+        <v>200.3120706125849</v>
       </c>
       <c r="Q38" t="n">
-        <v>561.0000000000001</v>
+        <v>561</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -37672,13 +37672,13 @@
         <v>311.6274301124894</v>
       </c>
       <c r="L39" t="n">
-        <v>436.150196103404</v>
+        <v>433.9385745190985</v>
       </c>
       <c r="M39" t="n">
         <v>276.0650421645042</v>
       </c>
       <c r="N39" t="n">
-        <v>326.5352398450737</v>
+        <v>328.7468614294096</v>
       </c>
       <c r="O39" t="n">
         <v>419.0391822801049</v>
@@ -37724,13 +37724,13 @@
         <v>57.88619966292134</v>
       </c>
       <c r="C40" t="n">
-        <v>72.27475335195533</v>
+        <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>59.46378194444452</v>
       </c>
       <c r="E40" t="n">
-        <v>64.01909516304346</v>
+        <v>0</v>
       </c>
       <c r="F40" t="n">
         <v>70.61714403225807</v>
@@ -37742,13 +37742,13 @@
         <v>121.7922509475617</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>187.184183724144</v>
       </c>
       <c r="J40" t="n">
-        <v>353.9707069017971</v>
+        <v>8.970706901797143</v>
       </c>
       <c r="K40" t="n">
-        <v>8.888852870420509</v>
+        <v>97.70504593304666</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -37781,7 +37781,7 @@
         <v>194.0757398730831</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>145.8296897837838</v>
       </c>
       <c r="W40" t="n">
         <v>118.6271901612903</v>
@@ -37824,19 +37824,19 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>513.658479084785</v>
+        <v>83.35374249862829</v>
       </c>
       <c r="K41" t="n">
         <v>177.4460351758794</v>
       </c>
       <c r="L41" t="n">
-        <v>220.1374974874373</v>
+        <v>473.4317817560116</v>
       </c>
       <c r="M41" t="n">
-        <v>383.9895476824594</v>
+        <v>561</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>561</v>
       </c>
       <c r="O41" t="n">
         <v>164.7897032902292</v>
@@ -37845,7 +37845,7 @@
         <v>200.3120706125849</v>
       </c>
       <c r="Q41" t="n">
-        <v>561.0000000000019</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -37915,7 +37915,7 @@
         <v>276.0650421645042</v>
       </c>
       <c r="N42" t="n">
-        <v>326.5352398450811</v>
+        <v>326.5352398451041</v>
       </c>
       <c r="O42" t="n">
         <v>419.0391822801049</v>
@@ -37961,13 +37961,13 @@
         <v>57.88619966292134</v>
       </c>
       <c r="C43" t="n">
-        <v>72.27475335195533</v>
+        <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>59.46378194444452</v>
+        <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>64.01909516304346</v>
+        <v>45.00349193130575</v>
       </c>
       <c r="F43" t="n">
         <v>70.61714403225807</v>
@@ -37982,10 +37982,10 @@
         <v>187.184183724144</v>
       </c>
       <c r="J43" t="n">
-        <v>8.970706901797143</v>
+        <v>353.9707069017971</v>
       </c>
       <c r="K43" t="n">
-        <v>97.95229014059346</v>
+        <v>129.178570461152</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -38015,19 +38015,19 @@
         <v>137.6490400511193</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>194.0757398730831</v>
       </c>
       <c r="V43" t="n">
-        <v>145.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>118.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>97.55635456989245</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>57.53464715053764</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -38061,19 +38061,19 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>83.35374249862829</v>
+        <v>513.658479084785</v>
       </c>
       <c r="K44" t="n">
-        <v>561.000000000011</v>
+        <v>177.4460351758794</v>
       </c>
       <c r="L44" t="n">
-        <v>561.0000000000111</v>
+        <v>220.1374974874373</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>561</v>
       </c>
       <c r="N44" t="n">
-        <v>89.87781693190874</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>164.7897032902292</v>
@@ -38082,7 +38082,7 @@
         <v>200.3120706125849</v>
       </c>
       <c r="Q44" t="n">
-        <v>561.0000000000038</v>
+        <v>383.9895476824175</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -38146,13 +38146,13 @@
         <v>311.6274301124894</v>
       </c>
       <c r="L45" t="n">
-        <v>436.150196103404</v>
+        <v>433.9385745190985</v>
       </c>
       <c r="M45" t="n">
         <v>276.0650421645042</v>
       </c>
       <c r="N45" t="n">
-        <v>326.5352398450884</v>
+        <v>328.7468614294096</v>
       </c>
       <c r="O45" t="n">
         <v>419.0391822801049</v>
@@ -38204,22 +38204,22 @@
         <v>59.46378194444452</v>
       </c>
       <c r="E46" t="n">
-        <v>64.01909516304346</v>
+        <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>70.61714403225807</v>
+        <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>100.581864863388</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>121.7922509475617</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
         <v>187.184183724144</v>
       </c>
       <c r="J46" t="n">
-        <v>8.970706901797143</v>
+        <v>281.287540445075</v>
       </c>
       <c r="K46" t="n">
         <v>129.178570461152</v>
@@ -38252,19 +38252,19 @@
         <v>137.6490400511193</v>
       </c>
       <c r="U46" t="n">
-        <v>100.1209064734635</v>
+        <v>194.0757398730831</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>145.8296897837838</v>
       </c>
       <c r="W46" t="n">
         <v>118.6271901612903</v>
       </c>
       <c r="X46" t="n">
-        <v>97.55635456989245</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>57.53464715053764</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
